--- a/research/traditional_assets/database/data/spain/spain_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_healthcare_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1130383703355893</v>
+        <v>0.1127895244097503</v>
       </c>
       <c r="C2">
-        <v>187.9481090171909</v>
+        <v>186.4425478656993</v>
       </c>
       <c r="D2">
-        <v>176.2481090171909</v>
+        <v>176.6425478656993</v>
       </c>
       <c r="E2">
-        <v>-20.5</v>
+        <v>-18.6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G2">
         <v>11.7</v>
@@ -1451,28 +1451,28 @@
         <v>10.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.09557</v>
       </c>
       <c r="N2">
-        <v>10.8</v>
+        <v>10.70443</v>
       </c>
       <c r="O2">
-        <v>2.7</v>
+        <v>2.6761075</v>
       </c>
       <c r="P2">
-        <v>8.100000000000001</v>
+        <v>8.0283225</v>
       </c>
       <c r="Q2">
-        <v>19.8</v>
+        <v>19.7283225</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1130383703355893</v>
+        <v>0.1135477519290407</v>
       </c>
       <c r="T2">
-        <v>1.040156204727314</v>
+        <v>1.048036175975249</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>113.0061734854034</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1127895244097503</v>
+        <v>0.1125406784839114</v>
       </c>
       <c r="C3">
-        <v>186.4425478656993</v>
+        <v>184.9387561626935</v>
       </c>
       <c r="D3">
-        <v>176.6425478656993</v>
+        <v>177.0387561626935</v>
       </c>
       <c r="E3">
-        <v>-18.6</v>
+        <v>-16.7</v>
       </c>
       <c r="F3">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="G3">
         <v>11.7</v>
@@ -1533,28 +1533,28 @@
         <v>10.8</v>
       </c>
       <c r="M3">
-        <v>0.09557</v>
+        <v>0.19114</v>
       </c>
       <c r="N3">
-        <v>10.70443</v>
+        <v>10.60886</v>
       </c>
       <c r="O3">
-        <v>2.6761075</v>
+        <v>2.652215</v>
       </c>
       <c r="P3">
-        <v>8.0283225</v>
+        <v>7.956645</v>
       </c>
       <c r="Q3">
-        <v>19.7283225</v>
+        <v>19.656645</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1135477519290407</v>
+        <v>0.1140675290652157</v>
       </c>
       <c r="T3">
-        <v>1.048036175975249</v>
+        <v>1.056076962962937</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>113.0061734854034</v>
+        <v>56.50308674270168</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1125406784839114</v>
+        <v>0.1122918325580724</v>
       </c>
       <c r="C4">
-        <v>184.9387561626935</v>
+        <v>183.4367458415309</v>
       </c>
       <c r="D4">
-        <v>177.0387561626935</v>
+        <v>177.4367458415309</v>
       </c>
       <c r="E4">
-        <v>-16.7</v>
+        <v>-14.8</v>
       </c>
       <c r="F4">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="G4">
         <v>11.7</v>
@@ -1615,28 +1615,28 @@
         <v>10.8</v>
       </c>
       <c r="M4">
-        <v>0.19114</v>
+        <v>0.28671</v>
       </c>
       <c r="N4">
-        <v>10.60886</v>
+        <v>10.51329</v>
       </c>
       <c r="O4">
-        <v>2.652215</v>
+        <v>2.6283225</v>
       </c>
       <c r="P4">
-        <v>7.956645</v>
+        <v>7.884967500000001</v>
       </c>
       <c r="Q4">
-        <v>19.656645</v>
+        <v>19.5849675</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1140675290652157</v>
+        <v>0.1145980232557447</v>
       </c>
       <c r="T4">
-        <v>1.056076962962937</v>
+        <v>1.064283539373051</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>56.50308674270168</v>
+        <v>37.66872449513446</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1122918325580724</v>
+        <v>0.1120429866322334</v>
       </c>
       <c r="C5">
-        <v>183.4367458415309</v>
+        <v>181.9365289431167</v>
       </c>
       <c r="D5">
-        <v>177.4367458415309</v>
+        <v>177.8365289431167</v>
       </c>
       <c r="E5">
-        <v>-14.8</v>
+        <v>-12.9</v>
       </c>
       <c r="F5">
-        <v>5.7</v>
+        <v>7.600000000000001</v>
       </c>
       <c r="G5">
         <v>11.7</v>
@@ -1697,28 +1697,28 @@
         <v>10.8</v>
       </c>
       <c r="M5">
-        <v>0.28671</v>
+        <v>0.38228</v>
       </c>
       <c r="N5">
-        <v>10.51329</v>
+        <v>10.41772</v>
       </c>
       <c r="O5">
-        <v>2.6283225</v>
+        <v>2.60443</v>
       </c>
       <c r="P5">
-        <v>7.884967500000001</v>
+        <v>7.81329</v>
       </c>
       <c r="Q5">
-        <v>19.5849675</v>
+        <v>19.51329</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1145980232557447</v>
+        <v>0.1151395694085765</v>
       </c>
       <c r="T5">
-        <v>1.064283539373051</v>
+        <v>1.072661086125043</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>37.66872449513446</v>
+        <v>28.25154337135085</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1120429866322334</v>
+        <v>0.1117941407063944</v>
       </c>
       <c r="C6">
-        <v>181.9365289431167</v>
+        <v>180.4381176171191</v>
       </c>
       <c r="D6">
-        <v>177.8365289431167</v>
+        <v>178.2381176171191</v>
       </c>
       <c r="E6">
-        <v>-12.9</v>
+        <v>-11</v>
       </c>
       <c r="F6">
-        <v>7.600000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="G6">
         <v>11.7</v>
@@ -1779,28 +1779,28 @@
         <v>10.8</v>
       </c>
       <c r="M6">
-        <v>0.38228</v>
+        <v>0.47785</v>
       </c>
       <c r="N6">
-        <v>10.41772</v>
+        <v>10.32215</v>
       </c>
       <c r="O6">
-        <v>2.60443</v>
+        <v>2.5805375</v>
       </c>
       <c r="P6">
-        <v>7.81329</v>
+        <v>7.7416125</v>
       </c>
       <c r="Q6">
-        <v>19.51329</v>
+        <v>19.4416125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1151395694085765</v>
+        <v>0.1156925165330468</v>
       </c>
       <c r="T6">
-        <v>1.072661086125043</v>
+        <v>1.08121500228234</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.25154337135085</v>
+        <v>22.60123469708067</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1117941407063944</v>
+        <v>0.1115452947805555</v>
       </c>
       <c r="C7">
-        <v>180.4381176171191</v>
+        <v>178.9415241231994</v>
       </c>
       <c r="D7">
-        <v>178.2381176171191</v>
+        <v>178.6415241231994</v>
       </c>
       <c r="E7">
-        <v>-11</v>
+        <v>-9.1</v>
       </c>
       <c r="F7">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
       <c r="G7">
         <v>11.7</v>
@@ -1861,28 +1861,28 @@
         <v>10.8</v>
       </c>
       <c r="M7">
-        <v>0.47785</v>
+        <v>0.57342</v>
       </c>
       <c r="N7">
-        <v>10.32215</v>
+        <v>10.22658</v>
       </c>
       <c r="O7">
-        <v>2.5805375</v>
+        <v>2.556645</v>
       </c>
       <c r="P7">
-        <v>7.7416125</v>
+        <v>7.669935000000001</v>
       </c>
       <c r="Q7">
-        <v>19.4416125</v>
+        <v>19.369935</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1156925165330468</v>
+        <v>0.1162572284899526</v>
       </c>
       <c r="T7">
-        <v>1.08121500228234</v>
+        <v>1.08995091665575</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.60123469708067</v>
+        <v>18.83436224756723</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1115452947805555</v>
+        <v>0.1112964488547165</v>
       </c>
       <c r="C8">
-        <v>178.9415241231994</v>
+        <v>177.4467608322601</v>
       </c>
       <c r="D8">
-        <v>178.6415241231994</v>
+        <v>179.0467608322602</v>
       </c>
       <c r="E8">
-        <v>-9.1</v>
+        <v>-7.200000000000001</v>
       </c>
       <c r="F8">
-        <v>11.4</v>
+        <v>13.3</v>
       </c>
       <c r="G8">
         <v>11.7</v>
@@ -1943,28 +1943,28 @@
         <v>10.8</v>
       </c>
       <c r="M8">
-        <v>0.57342</v>
+        <v>0.6689899999999999</v>
       </c>
       <c r="N8">
-        <v>10.22658</v>
+        <v>10.13101</v>
       </c>
       <c r="O8">
-        <v>2.556645</v>
+        <v>2.5327525</v>
       </c>
       <c r="P8">
-        <v>7.669935000000001</v>
+        <v>7.598257500000001</v>
       </c>
       <c r="Q8">
-        <v>19.369935</v>
+        <v>19.2982575</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1162572284899526</v>
+        <v>0.1168340847900177</v>
       </c>
       <c r="T8">
-        <v>1.08995091665575</v>
+        <v>1.098874700155469</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.83436224756723</v>
+        <v>16.14373906934334</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1112964488547165</v>
+        <v>0.1110476029288775</v>
       </c>
       <c r="C9">
-        <v>177.4467608322601</v>
+        <v>175.9538402277093</v>
       </c>
       <c r="D9">
-        <v>179.0467608322602</v>
+        <v>179.4538402277093</v>
       </c>
       <c r="E9">
-        <v>-7.199999999999999</v>
+        <v>-5.299999999999999</v>
       </c>
       <c r="F9">
-        <v>13.3</v>
+        <v>15.2</v>
       </c>
       <c r="G9">
         <v>11.7</v>
@@ -2025,28 +2025,28 @@
         <v>10.8</v>
       </c>
       <c r="M9">
-        <v>0.66899</v>
+        <v>0.76456</v>
       </c>
       <c r="N9">
-        <v>10.13101</v>
+        <v>10.03544</v>
       </c>
       <c r="O9">
-        <v>2.5327525</v>
+        <v>2.50886</v>
       </c>
       <c r="P9">
-        <v>7.5982575</v>
+        <v>7.526580000000001</v>
       </c>
       <c r="Q9">
-        <v>19.2982575</v>
+        <v>19.22658</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1168340847900177</v>
+        <v>0.1174234814444321</v>
       </c>
       <c r="T9">
-        <v>1.098874700155469</v>
+        <v>1.107992478948661</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.14373906934334</v>
+        <v>14.12577168567542</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1110476029288775</v>
+        <v>0.1109000070030385</v>
       </c>
       <c r="C10">
-        <v>175.9538402277093</v>
+        <v>174.2961635934487</v>
       </c>
       <c r="D10">
-        <v>179.4538402277093</v>
+        <v>179.6961635934487</v>
       </c>
       <c r="E10">
-        <v>-5.299999999999999</v>
+        <v>-3.400000000000002</v>
       </c>
       <c r="F10">
-        <v>15.2</v>
+        <v>17.1</v>
       </c>
       <c r="G10">
         <v>11.7</v>
@@ -2107,45 +2107,45 @@
         <v>10.8</v>
       </c>
       <c r="M10">
-        <v>0.76456</v>
+        <v>0.8857799999999999</v>
       </c>
       <c r="N10">
-        <v>10.03544</v>
+        <v>9.91422</v>
       </c>
       <c r="O10">
-        <v>2.50886</v>
+        <v>2.478555</v>
       </c>
       <c r="P10">
-        <v>7.526580000000001</v>
+        <v>7.435665</v>
       </c>
       <c r="Q10">
-        <v>19.22658</v>
+        <v>19.135665</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1174234814444321</v>
+        <v>0.1180258318714709</v>
       </c>
       <c r="T10">
-        <v>1.107992478948661</v>
+        <v>1.11731064848456</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>14.12577168567542</v>
+        <v>12.19264377159114</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1109000070030385</v>
+        <v>0.1106624110771996</v>
       </c>
       <c r="C11">
-        <v>174.2961635934487</v>
+        <v>172.7876268736517</v>
       </c>
       <c r="D11">
-        <v>179.6961635934487</v>
+        <v>180.0876268736517</v>
       </c>
       <c r="E11">
-        <v>-3.400000000000002</v>
+        <v>-1.5</v>
       </c>
       <c r="F11">
-        <v>17.1</v>
+        <v>19</v>
       </c>
       <c r="G11">
         <v>11.7</v>
@@ -2189,28 +2189,28 @@
         <v>10.8</v>
       </c>
       <c r="M11">
-        <v>0.8857799999999999</v>
+        <v>0.9842</v>
       </c>
       <c r="N11">
-        <v>9.91422</v>
+        <v>9.815800000000001</v>
       </c>
       <c r="O11">
-        <v>2.478555</v>
+        <v>2.45395</v>
       </c>
       <c r="P11">
-        <v>7.435665</v>
+        <v>7.36185</v>
       </c>
       <c r="Q11">
-        <v>19.135665</v>
+        <v>19.06185</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1180258318714709</v>
+        <v>0.1186415678635551</v>
       </c>
       <c r="T11">
-        <v>1.11731064848456</v>
+        <v>1.12683588845459</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.19264377159114</v>
+        <v>10.97337939443203</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1106624110771996</v>
+        <v>0.1104248151513606</v>
       </c>
       <c r="C12">
-        <v>172.7876268736517</v>
+        <v>171.2807994620823</v>
       </c>
       <c r="D12">
-        <v>180.0876268736517</v>
+        <v>180.4807994620824</v>
       </c>
       <c r="E12">
-        <v>-1.5</v>
+        <v>0.3999999999999986</v>
       </c>
       <c r="F12">
-        <v>19</v>
+        <v>20.9</v>
       </c>
       <c r="G12">
         <v>11.7</v>
@@ -2271,28 +2271,28 @@
         <v>10.8</v>
       </c>
       <c r="M12">
-        <v>0.9842</v>
+        <v>1.08262</v>
       </c>
       <c r="N12">
-        <v>9.815800000000001</v>
+        <v>9.71738</v>
       </c>
       <c r="O12">
-        <v>2.45395</v>
+        <v>2.429345</v>
       </c>
       <c r="P12">
-        <v>7.36185</v>
+        <v>7.288035000000001</v>
       </c>
       <c r="Q12">
-        <v>19.06185</v>
+        <v>18.988035</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1186415678635551</v>
+        <v>0.1192711406195063</v>
       </c>
       <c r="T12">
-        <v>1.12683588845459</v>
+        <v>1.136575178761026</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>10.97337939443203</v>
+        <v>9.975799449483661</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1104248151513606</v>
+        <v>0.1103402192255216</v>
       </c>
       <c r="C13">
-        <v>171.2807994620823</v>
+        <v>169.5212031598724</v>
       </c>
       <c r="D13">
-        <v>180.4807994620824</v>
+        <v>180.6212031598725</v>
       </c>
       <c r="E13">
-        <v>0.3999999999999986</v>
+        <v>2.300000000000001</v>
       </c>
       <c r="F13">
-        <v>20.9</v>
+        <v>22.8</v>
       </c>
       <c r="G13">
         <v>11.7</v>
@@ -2353,45 +2353,45 @@
         <v>10.8</v>
       </c>
       <c r="M13">
-        <v>1.08262</v>
+        <v>1.2198</v>
       </c>
       <c r="N13">
-        <v>9.71738</v>
+        <v>9.580200000000001</v>
       </c>
       <c r="O13">
-        <v>2.429345</v>
+        <v>2.39505</v>
       </c>
       <c r="P13">
-        <v>7.288035000000001</v>
+        <v>7.185150000000001</v>
       </c>
       <c r="Q13">
-        <v>18.988035</v>
+        <v>18.88515</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1192711406195063</v>
+        <v>0.1199150218471837</v>
       </c>
       <c r="T13">
-        <v>1.136575178761026</v>
+        <v>1.146535816574426</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>9.975799449483661</v>
+        <v>8.8539104771274</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1103402192255216</v>
+        <v>0.1101153732996827</v>
       </c>
       <c r="C14">
-        <v>169.5212031598724</v>
+        <v>167.9954436358079</v>
       </c>
       <c r="D14">
-        <v>180.6212031598725</v>
+        <v>180.9954436358079</v>
       </c>
       <c r="E14">
-        <v>2.300000000000001</v>
+        <v>4.199999999999999</v>
       </c>
       <c r="F14">
-        <v>22.8</v>
+        <v>24.7</v>
       </c>
       <c r="G14">
         <v>11.7</v>
@@ -2435,28 +2435,28 @@
         <v>10.8</v>
       </c>
       <c r="M14">
-        <v>1.2198</v>
+        <v>1.32145</v>
       </c>
       <c r="N14">
-        <v>9.580200000000001</v>
+        <v>9.47855</v>
       </c>
       <c r="O14">
-        <v>2.39505</v>
+        <v>2.3696375</v>
       </c>
       <c r="P14">
-        <v>7.185150000000001</v>
+        <v>7.108912500000001</v>
       </c>
       <c r="Q14">
-        <v>18.88515</v>
+        <v>18.8089125</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1199150218471837</v>
+        <v>0.120573704942164</v>
       </c>
       <c r="T14">
-        <v>1.146535816574426</v>
+        <v>1.156725434567444</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.8539104771274</v>
+        <v>8.17284044042529</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1101153732996827</v>
+        <v>0.1099745273738437</v>
       </c>
       <c r="C15">
-        <v>167.9954436358079</v>
+        <v>166.3306629456034</v>
       </c>
       <c r="D15">
-        <v>180.9954436358079</v>
+        <v>181.2306629456034</v>
       </c>
       <c r="E15">
-        <v>4.199999999999999</v>
+        <v>6.100000000000001</v>
       </c>
       <c r="F15">
-        <v>24.7</v>
+        <v>26.6</v>
       </c>
       <c r="G15">
         <v>11.7</v>
@@ -2517,45 +2517,45 @@
         <v>10.8</v>
       </c>
       <c r="M15">
-        <v>1.32145</v>
+        <v>1.44438</v>
       </c>
       <c r="N15">
-        <v>9.47855</v>
+        <v>9.35562</v>
       </c>
       <c r="O15">
-        <v>2.3696375</v>
+        <v>2.338905</v>
       </c>
       <c r="P15">
-        <v>7.108912500000001</v>
+        <v>7.016715</v>
       </c>
       <c r="Q15">
-        <v>18.8089125</v>
+        <v>18.716715</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.120573704942164</v>
+        <v>0.1212477062486554</v>
       </c>
       <c r="T15">
-        <v>1.156725434567444</v>
+        <v>1.167152020420765</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>8.17284044042529</v>
+        <v>7.477256677605617</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1099745273738437</v>
+        <v>0.1097556814480047</v>
       </c>
       <c r="C16">
-        <v>166.3306629456034</v>
+        <v>164.7973613667394</v>
       </c>
       <c r="D16">
-        <v>181.2306629456034</v>
+        <v>181.5973613667394</v>
       </c>
       <c r="E16">
-        <v>6.100000000000001</v>
+        <v>8.000000000000004</v>
       </c>
       <c r="F16">
-        <v>26.6</v>
+        <v>28.5</v>
       </c>
       <c r="G16">
         <v>11.7</v>
@@ -2599,28 +2599,28 @@
         <v>10.8</v>
       </c>
       <c r="M16">
-        <v>1.44438</v>
+        <v>1.54755</v>
       </c>
       <c r="N16">
-        <v>9.35562</v>
+        <v>9.25245</v>
       </c>
       <c r="O16">
-        <v>2.338905</v>
+        <v>2.3131125</v>
       </c>
       <c r="P16">
-        <v>7.016715</v>
+        <v>6.9393375</v>
       </c>
       <c r="Q16">
-        <v>18.716715</v>
+        <v>18.6393375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1212477062486554</v>
+        <v>0.1219375664094173</v>
       </c>
       <c r="T16">
-        <v>1.167152020420765</v>
+        <v>1.177823937705929</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.477256677605617</v>
+        <v>6.978772899098574</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1097556814480047</v>
+        <v>0.1095368355221657</v>
       </c>
       <c r="C17">
-        <v>164.7973613667394</v>
+        <v>163.2655467367257</v>
       </c>
       <c r="D17">
-        <v>181.5973613667394</v>
+        <v>181.9655467367257</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>9.900000000000002</v>
       </c>
       <c r="F17">
-        <v>28.5</v>
+        <v>30.4</v>
       </c>
       <c r="G17">
         <v>11.7</v>
@@ -2681,28 +2681,28 @@
         <v>10.8</v>
       </c>
       <c r="M17">
-        <v>1.54755</v>
+        <v>1.65072</v>
       </c>
       <c r="N17">
-        <v>9.252450000000001</v>
+        <v>9.149280000000001</v>
       </c>
       <c r="O17">
-        <v>2.3131125</v>
+        <v>2.28732</v>
       </c>
       <c r="P17">
-        <v>6.939337500000001</v>
+        <v>6.861960000000001</v>
       </c>
       <c r="Q17">
-        <v>18.6393375</v>
+        <v>18.56196</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1219375664094173</v>
+        <v>0.1226438518121021</v>
       </c>
       <c r="T17">
-        <v>1.177823937705929</v>
+        <v>1.188749948259788</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.978772899098576</v>
+        <v>6.542599592904915</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1095368355221657</v>
+        <v>0.1093179895963268</v>
       </c>
       <c r="C18">
-        <v>163.2655467367257</v>
+        <v>161.7352281182226</v>
       </c>
       <c r="D18">
-        <v>181.9655467367257</v>
+        <v>182.3352281182226</v>
       </c>
       <c r="E18">
-        <v>9.900000000000002</v>
+        <v>11.8</v>
       </c>
       <c r="F18">
-        <v>30.4</v>
+        <v>32.3</v>
       </c>
       <c r="G18">
         <v>11.7</v>
@@ -2763,28 +2763,28 @@
         <v>10.8</v>
       </c>
       <c r="M18">
-        <v>1.65072</v>
+        <v>1.75389</v>
       </c>
       <c r="N18">
-        <v>9.149280000000001</v>
+        <v>9.046110000000001</v>
       </c>
       <c r="O18">
-        <v>2.28732</v>
+        <v>2.2615275</v>
       </c>
       <c r="P18">
-        <v>6.861960000000001</v>
+        <v>6.784582500000001</v>
       </c>
       <c r="Q18">
-        <v>18.56196</v>
+        <v>18.4845825</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1226438518121021</v>
+        <v>0.1233671561401527</v>
       </c>
       <c r="T18">
-        <v>1.188749948259788</v>
+        <v>1.19993923617639</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.542599592904915</v>
+        <v>6.157740793322272</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1093179895963268</v>
+        <v>0.1092341436704878</v>
       </c>
       <c r="C19">
-        <v>161.7352281182226</v>
+        <v>159.9772615777592</v>
       </c>
       <c r="D19">
-        <v>182.3352281182226</v>
+        <v>182.4772615777593</v>
       </c>
       <c r="E19">
-        <v>11.8</v>
+        <v>13.7</v>
       </c>
       <c r="F19">
-        <v>32.3</v>
+        <v>34.2</v>
       </c>
       <c r="G19">
         <v>11.7</v>
@@ -2845,45 +2845,45 @@
         <v>10.8</v>
       </c>
       <c r="M19">
-        <v>1.75389</v>
+        <v>1.89126</v>
       </c>
       <c r="N19">
-        <v>9.046110000000001</v>
+        <v>8.90874</v>
       </c>
       <c r="O19">
-        <v>2.2615275</v>
+        <v>2.227185</v>
       </c>
       <c r="P19">
-        <v>6.784582500000001</v>
+        <v>6.681554999999999</v>
       </c>
       <c r="Q19">
-        <v>18.4845825</v>
+        <v>18.381555</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1233671561401527</v>
+        <v>0.1241081020371802</v>
       </c>
       <c r="T19">
-        <v>1.19993923617639</v>
+        <v>1.211401433554372</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.157740793322272</v>
+        <v>5.710478728466736</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1092341436704878</v>
+        <v>0.1090227977446488</v>
       </c>
       <c r="C20">
-        <v>159.9772615777592</v>
+        <v>158.4362614787466</v>
       </c>
       <c r="D20">
-        <v>182.4772615777592</v>
+        <v>182.8362614787466</v>
       </c>
       <c r="E20">
-        <v>13.7</v>
+        <v>15.6</v>
       </c>
       <c r="F20">
-        <v>34.2</v>
+        <v>36.1</v>
       </c>
       <c r="G20">
         <v>11.7</v>
@@ -2927,28 +2927,28 @@
         <v>10.8</v>
       </c>
       <c r="M20">
-        <v>1.89126</v>
+        <v>1.99633</v>
       </c>
       <c r="N20">
-        <v>8.908740000000002</v>
+        <v>8.80367</v>
       </c>
       <c r="O20">
-        <v>2.227185</v>
+        <v>2.2009175</v>
       </c>
       <c r="P20">
-        <v>6.681555000000001</v>
+        <v>6.6027525</v>
       </c>
       <c r="Q20">
-        <v>18.381555</v>
+        <v>18.3027525</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1241081020371802</v>
+        <v>0.1248673428946282</v>
       </c>
       <c r="T20">
-        <v>1.211401433554372</v>
+        <v>1.223146648151564</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.710478728466738</v>
+        <v>5.409927216442171</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1090227977446488</v>
+        <v>0.1088114518188098</v>
       </c>
       <c r="C21">
-        <v>158.4362614787466</v>
+        <v>156.8966767339959</v>
       </c>
       <c r="D21">
-        <v>182.8362614787466</v>
+        <v>183.1966767339959</v>
       </c>
       <c r="E21">
-        <v>15.6</v>
+        <v>17.5</v>
       </c>
       <c r="F21">
-        <v>36.1</v>
+        <v>38</v>
       </c>
       <c r="G21">
         <v>11.7</v>
@@ -3009,28 +3009,28 @@
         <v>10.8</v>
       </c>
       <c r="M21">
-        <v>1.99633</v>
+        <v>2.1014</v>
       </c>
       <c r="N21">
-        <v>8.80367</v>
+        <v>8.698600000000001</v>
       </c>
       <c r="O21">
-        <v>2.2009175</v>
+        <v>2.17465</v>
       </c>
       <c r="P21">
-        <v>6.6027525</v>
+        <v>6.523950000000001</v>
       </c>
       <c r="Q21">
-        <v>18.3027525</v>
+        <v>18.22395</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1248673428946282</v>
+        <v>0.1256455647735123</v>
       </c>
       <c r="T21">
-        <v>1.223146648151564</v>
+        <v>1.235185493113686</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.409927216442171</v>
+        <v>5.139430855620064</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1088114518188098</v>
+        <v>0.1086001058929709</v>
       </c>
       <c r="C22">
-        <v>156.8966767339959</v>
+        <v>155.3585157300733</v>
       </c>
       <c r="D22">
-        <v>183.1966767339959</v>
+        <v>183.5585157300734</v>
       </c>
       <c r="E22">
-        <v>17.5</v>
+        <v>19.40000000000001</v>
       </c>
       <c r="F22">
-        <v>38</v>
+        <v>39.90000000000001</v>
       </c>
       <c r="G22">
         <v>11.7</v>
@@ -3091,28 +3091,28 @@
         <v>10.8</v>
       </c>
       <c r="M22">
-        <v>2.1014</v>
+        <v>2.20647</v>
       </c>
       <c r="N22">
-        <v>8.698600000000001</v>
+        <v>8.593530000000001</v>
       </c>
       <c r="O22">
-        <v>2.17465</v>
+        <v>2.1483825</v>
       </c>
       <c r="P22">
-        <v>6.523950000000001</v>
+        <v>6.445147500000001</v>
       </c>
       <c r="Q22">
-        <v>18.22395</v>
+        <v>18.1451475</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1256455647735123</v>
+        <v>0.126443488472115</v>
       </c>
       <c r="T22">
-        <v>1.235185493113686</v>
+        <v>1.247529118960924</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.139430855620064</v>
+        <v>4.894696052971488</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1086001058929709</v>
+        <v>0.1083887599671319</v>
       </c>
       <c r="C23">
-        <v>155.3585157300733</v>
+        <v>153.8217869199352</v>
       </c>
       <c r="D23">
-        <v>183.5585157300734</v>
+        <v>183.9217869199352</v>
       </c>
       <c r="E23">
-        <v>19.4</v>
+        <v>21.3</v>
       </c>
       <c r="F23">
-        <v>39.9</v>
+        <v>41.8</v>
       </c>
       <c r="G23">
         <v>11.7</v>
@@ -3173,28 +3173,28 @@
         <v>10.8</v>
       </c>
       <c r="M23">
-        <v>2.20647</v>
+        <v>2.31154</v>
       </c>
       <c r="N23">
-        <v>8.593530000000001</v>
+        <v>8.48846</v>
       </c>
       <c r="O23">
-        <v>2.1483825</v>
+        <v>2.122115</v>
       </c>
       <c r="P23">
-        <v>6.445147500000001</v>
+        <v>6.366345</v>
       </c>
       <c r="Q23">
-        <v>18.1451475</v>
+        <v>18.066345</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.126443488472115</v>
+        <v>0.1272618717527332</v>
       </c>
       <c r="T23">
-        <v>1.247529118960924</v>
+        <v>1.260189248035015</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.894696052971489</v>
+        <v>4.672209868745512</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1083887599671319</v>
+        <v>0.1086086640412929</v>
       </c>
       <c r="C24">
-        <v>153.8217869199352</v>
+        <v>151.5438358160831</v>
       </c>
       <c r="D24">
-        <v>183.9217869199352</v>
+        <v>183.5438358160831</v>
       </c>
       <c r="E24">
-        <v>21.3</v>
+        <v>23.2</v>
       </c>
       <c r="F24">
-        <v>41.8</v>
+        <v>43.7</v>
       </c>
       <c r="G24">
         <v>11.7</v>
@@ -3255,45 +3255,45 @@
         <v>10.8</v>
       </c>
       <c r="M24">
-        <v>2.31154</v>
+        <v>2.52586</v>
       </c>
       <c r="N24">
-        <v>8.48846</v>
+        <v>8.274140000000001</v>
       </c>
       <c r="O24">
-        <v>2.122115</v>
+        <v>2.068535</v>
       </c>
       <c r="P24">
-        <v>6.366345</v>
+        <v>6.205605</v>
       </c>
       <c r="Q24">
-        <v>18.066345</v>
+        <v>17.905605</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1272618717527332</v>
+        <v>0.1281015117419388</v>
       </c>
       <c r="T24">
-        <v>1.260189248035015</v>
+        <v>1.273178211630511</v>
       </c>
       <c r="U24">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.672209868745512</v>
+        <v>4.275771420427102</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1086086640412929</v>
+        <v>0.1084160681154539</v>
       </c>
       <c r="C25">
-        <v>151.5438358160831</v>
+        <v>149.974767536648</v>
       </c>
       <c r="D25">
-        <v>183.5438358160831</v>
+        <v>183.874767536648</v>
       </c>
       <c r="E25">
-        <v>23.2</v>
+        <v>25.1</v>
       </c>
       <c r="F25">
-        <v>43.7</v>
+        <v>45.6</v>
       </c>
       <c r="G25">
         <v>11.7</v>
@@ -3337,28 +3337,28 @@
         <v>10.8</v>
       </c>
       <c r="M25">
-        <v>2.52586</v>
+        <v>2.63568</v>
       </c>
       <c r="N25">
-        <v>8.274140000000001</v>
+        <v>8.16432</v>
       </c>
       <c r="O25">
-        <v>2.068535</v>
+        <v>2.04108</v>
       </c>
       <c r="P25">
-        <v>6.205605</v>
+        <v>6.12324</v>
       </c>
       <c r="Q25">
-        <v>17.905605</v>
+        <v>17.82324</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1281015117419388</v>
+        <v>0.1289632475203341</v>
       </c>
       <c r="T25">
-        <v>1.273178211630511</v>
+        <v>1.286508990057468</v>
       </c>
       <c r="U25">
         <v>0.0578</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.275771420427102</v>
+        <v>4.097614277909306</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1084160681154539</v>
+        <v>0.1088797221896149</v>
       </c>
       <c r="C26">
-        <v>149.974767536648</v>
+        <v>147.2800977275975</v>
       </c>
       <c r="D26">
-        <v>183.874767536648</v>
+        <v>183.0800977275975</v>
       </c>
       <c r="E26">
-        <v>25.1</v>
+        <v>27</v>
       </c>
       <c r="F26">
-        <v>45.6</v>
+        <v>47.5</v>
       </c>
       <c r="G26">
         <v>11.7</v>
@@ -3419,45 +3419,45 @@
         <v>10.8</v>
       </c>
       <c r="M26">
-        <v>2.63568</v>
+        <v>2.91175</v>
       </c>
       <c r="N26">
-        <v>8.16432</v>
+        <v>7.888250000000001</v>
       </c>
       <c r="O26">
-        <v>2.04108</v>
+        <v>1.9720625</v>
       </c>
       <c r="P26">
-        <v>6.12324</v>
+        <v>5.916187500000001</v>
       </c>
       <c r="Q26">
-        <v>17.82324</v>
+        <v>17.6161875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1289632475203341</v>
+        <v>0.1298479629194866</v>
       </c>
       <c r="T26">
-        <v>1.286508990057468</v>
+        <v>1.300195255909143</v>
       </c>
       <c r="U26">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.097614277909306</v>
+        <v>3.709109641967889</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1088797221896149</v>
+        <v>0.108713376263776</v>
       </c>
       <c r="C27">
-        <v>147.2800977275975</v>
+        <v>145.6644113796239</v>
       </c>
       <c r="D27">
-        <v>183.0800977275975</v>
+        <v>183.3644113796239</v>
       </c>
       <c r="E27">
-        <v>27</v>
+        <v>28.9</v>
       </c>
       <c r="F27">
-        <v>47.5</v>
+        <v>49.4</v>
       </c>
       <c r="G27">
         <v>11.7</v>
@@ -3501,28 +3501,28 @@
         <v>10.8</v>
       </c>
       <c r="M27">
-        <v>2.91175</v>
+        <v>3.02822</v>
       </c>
       <c r="N27">
-        <v>7.888250000000001</v>
+        <v>7.771780000000001</v>
       </c>
       <c r="O27">
-        <v>1.9720625</v>
+        <v>1.942945</v>
       </c>
       <c r="P27">
-        <v>5.916187500000001</v>
+        <v>5.828835000000001</v>
       </c>
       <c r="Q27">
-        <v>17.6161875</v>
+        <v>17.528835</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1298479629194866</v>
+        <v>0.1307565895456432</v>
       </c>
       <c r="T27">
-        <v>1.300195255909143</v>
+        <v>1.31425142083789</v>
       </c>
       <c r="U27">
         <v>0.0613</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.709109641967889</v>
+        <v>3.566451578815278</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.108713376263776</v>
+        <v>0.109114030337937</v>
       </c>
       <c r="C28">
-        <v>145.6644113796239</v>
+        <v>143.081117340032</v>
       </c>
       <c r="D28">
-        <v>183.3644113796239</v>
+        <v>182.681117340032</v>
       </c>
       <c r="E28">
-        <v>28.9</v>
+        <v>30.8</v>
       </c>
       <c r="F28">
-        <v>49.4</v>
+        <v>51.3</v>
       </c>
       <c r="G28">
         <v>11.7</v>
@@ -3583,45 +3583,45 @@
         <v>10.8</v>
       </c>
       <c r="M28">
-        <v>3.02822</v>
+        <v>3.288330000000001</v>
       </c>
       <c r="N28">
-        <v>7.771780000000001</v>
+        <v>7.511670000000001</v>
       </c>
       <c r="O28">
-        <v>1.942945</v>
+        <v>1.8779175</v>
       </c>
       <c r="P28">
-        <v>5.828835000000001</v>
+        <v>5.6337525</v>
       </c>
       <c r="Q28">
-        <v>17.528835</v>
+        <v>17.3337525</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1307565895456432</v>
+        <v>0.1316901100519685</v>
       </c>
       <c r="T28">
-        <v>1.31425142083789</v>
+        <v>1.328692686175645</v>
       </c>
       <c r="U28">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.566451578815278</v>
+        <v>3.284341899991789</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.109114030337937</v>
+        <v>0.1089686844120981</v>
       </c>
       <c r="C29">
-        <v>143.081117340032</v>
+        <v>141.4284076146743</v>
       </c>
       <c r="D29">
-        <v>182.681117340032</v>
+        <v>182.9284076146743</v>
       </c>
       <c r="E29">
-        <v>30.8</v>
+        <v>32.7</v>
       </c>
       <c r="F29">
-        <v>51.3</v>
+        <v>53.2</v>
       </c>
       <c r="G29">
         <v>11.7</v>
@@ -3665,28 +3665,28 @@
         <v>10.8</v>
       </c>
       <c r="M29">
-        <v>3.288330000000001</v>
+        <v>3.41012</v>
       </c>
       <c r="N29">
-        <v>7.511670000000001</v>
+        <v>7.38988</v>
       </c>
       <c r="O29">
-        <v>1.8779175</v>
+        <v>1.84747</v>
       </c>
       <c r="P29">
-        <v>5.6337525</v>
+        <v>5.54241</v>
       </c>
       <c r="Q29">
-        <v>17.3337525</v>
+        <v>17.24241</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1316901100519685</v>
+        <v>0.1326495616834695</v>
       </c>
       <c r="T29">
-        <v>1.328692686175645</v>
+        <v>1.343535097772781</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.284341899991789</v>
+        <v>3.167043974992082</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1089686844120981</v>
+        <v>0.1088233384862591</v>
       </c>
       <c r="C30">
-        <v>141.4284076146743</v>
+        <v>139.7763682965642</v>
       </c>
       <c r="D30">
-        <v>182.9284076146743</v>
+        <v>183.1763682965642</v>
       </c>
       <c r="E30">
-        <v>32.7</v>
+        <v>34.60000000000001</v>
       </c>
       <c r="F30">
-        <v>53.2</v>
+        <v>55.10000000000001</v>
       </c>
       <c r="G30">
         <v>11.7</v>
@@ -3747,28 +3747,28 @@
         <v>10.8</v>
       </c>
       <c r="M30">
-        <v>3.41012</v>
+        <v>3.531910000000001</v>
       </c>
       <c r="N30">
-        <v>7.38988</v>
+        <v>7.26809</v>
       </c>
       <c r="O30">
-        <v>1.84747</v>
+        <v>1.8170225</v>
       </c>
       <c r="P30">
-        <v>5.54241</v>
+        <v>5.4510675</v>
       </c>
       <c r="Q30">
-        <v>17.24241</v>
+        <v>17.1510675</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1326495616834695</v>
+        <v>0.1336360401214916</v>
       </c>
       <c r="T30">
-        <v>1.343535097772781</v>
+        <v>1.358795605471245</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.167043974992082</v>
+        <v>3.05783556206132</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1088233384862591</v>
+        <v>0.1104329925604201</v>
       </c>
       <c r="C31">
-        <v>139.7763682965642</v>
+        <v>135.1672390007614</v>
       </c>
       <c r="D31">
-        <v>183.1763682965642</v>
+        <v>180.4672390007614</v>
       </c>
       <c r="E31">
-        <v>34.59999999999999</v>
+        <v>36.5</v>
       </c>
       <c r="F31">
-        <v>55.09999999999999</v>
+        <v>57</v>
       </c>
       <c r="G31">
         <v>11.7</v>
@@ -3829,45 +3829,45 @@
         <v>10.8</v>
       </c>
       <c r="M31">
-        <v>3.53191</v>
+        <v>4.0983</v>
       </c>
       <c r="N31">
-        <v>7.268090000000001</v>
+        <v>6.701700000000001</v>
       </c>
       <c r="O31">
-        <v>1.8170225</v>
+        <v>1.675425</v>
       </c>
       <c r="P31">
-        <v>5.451067500000001</v>
+        <v>5.026275</v>
       </c>
       <c r="Q31">
-        <v>17.1510675</v>
+        <v>16.726275</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1336360401214916</v>
+        <v>0.134650703657743</v>
       </c>
       <c r="T31">
-        <v>1.358795605471245</v>
+        <v>1.37449212767538</v>
       </c>
       <c r="U31">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.057835562061321</v>
+        <v>2.635239001537223</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1104329925604201</v>
+        <v>0.1103461466345811</v>
       </c>
       <c r="C32">
-        <v>135.1672390007614</v>
+        <v>133.411358333742</v>
       </c>
       <c r="D32">
-        <v>180.4672390007614</v>
+        <v>180.611358333742</v>
       </c>
       <c r="E32">
-        <v>36.5</v>
+        <v>38.4</v>
       </c>
       <c r="F32">
-        <v>57</v>
+        <v>58.9</v>
       </c>
       <c r="G32">
         <v>11.7</v>
@@ -3911,28 +3911,28 @@
         <v>10.8</v>
       </c>
       <c r="M32">
-        <v>4.0983</v>
+        <v>4.23491</v>
       </c>
       <c r="N32">
-        <v>6.701700000000001</v>
+        <v>6.565090000000001</v>
       </c>
       <c r="O32">
-        <v>1.675425</v>
+        <v>1.6412725</v>
       </c>
       <c r="P32">
-        <v>5.026275</v>
+        <v>4.9238175</v>
       </c>
       <c r="Q32">
-        <v>16.726275</v>
+        <v>16.6238175</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.134650703657743</v>
+        <v>0.135694777731277</v>
       </c>
       <c r="T32">
-        <v>1.37449212767538</v>
+        <v>1.390643621537605</v>
       </c>
       <c r="U32">
         <v>0.07190000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.635239001537223</v>
+        <v>2.550231291810216</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1103461466345811</v>
+        <v>0.1111953007087421</v>
       </c>
       <c r="C33">
-        <v>133.411358333742</v>
+        <v>130.1120029872297</v>
       </c>
       <c r="D33">
-        <v>180.611358333742</v>
+        <v>179.2120029872297</v>
       </c>
       <c r="E33">
-        <v>38.4</v>
+        <v>40.3</v>
       </c>
       <c r="F33">
-        <v>58.9</v>
+        <v>60.8</v>
       </c>
       <c r="G33">
         <v>11.7</v>
@@ -3993,45 +3993,45 @@
         <v>10.8</v>
       </c>
       <c r="M33">
-        <v>4.23491</v>
+        <v>4.60864</v>
       </c>
       <c r="N33">
-        <v>6.565090000000001</v>
+        <v>6.19136</v>
       </c>
       <c r="O33">
-        <v>1.6412725</v>
+        <v>1.54784</v>
       </c>
       <c r="P33">
-        <v>4.9238175</v>
+        <v>4.643520000000001</v>
       </c>
       <c r="Q33">
-        <v>16.6238175</v>
+        <v>16.34352</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.135694777731277</v>
+        <v>0.1367695598657973</v>
       </c>
       <c r="T33">
-        <v>1.390643621537605</v>
+        <v>1.407270159336955</v>
       </c>
       <c r="U33">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.550231291810216</v>
+        <v>2.343424524371615</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1111953007087421</v>
+        <v>0.1111377047829032</v>
       </c>
       <c r="C34">
-        <v>130.1120029872297</v>
+        <v>128.306231774653</v>
       </c>
       <c r="D34">
-        <v>179.2120029872297</v>
+        <v>179.306231774653</v>
       </c>
       <c r="E34">
-        <v>40.3</v>
+        <v>42.2</v>
       </c>
       <c r="F34">
-        <v>60.8</v>
+        <v>62.7</v>
       </c>
       <c r="G34">
         <v>11.7</v>
@@ -4075,28 +4075,28 @@
         <v>10.8</v>
       </c>
       <c r="M34">
-        <v>4.60864</v>
+        <v>4.752660000000001</v>
       </c>
       <c r="N34">
-        <v>6.19136</v>
+        <v>6.04734</v>
       </c>
       <c r="O34">
-        <v>1.54784</v>
+        <v>1.511835</v>
       </c>
       <c r="P34">
-        <v>4.643520000000001</v>
+        <v>4.535505000000001</v>
       </c>
       <c r="Q34">
-        <v>16.34352</v>
+        <v>16.235505</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1367695598657973</v>
+        <v>0.1378764250491092</v>
       </c>
       <c r="T34">
-        <v>1.407270159336955</v>
+        <v>1.424393011697479</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.343424524371615</v>
+        <v>2.272411659996718</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1111377047829032</v>
+        <v>0.1110801088570642</v>
       </c>
       <c r="C35">
-        <v>128.306231774653</v>
+        <v>126.5005597042684</v>
       </c>
       <c r="D35">
-        <v>179.306231774653</v>
+        <v>179.4005597042684</v>
       </c>
       <c r="E35">
-        <v>42.2</v>
+        <v>44.10000000000001</v>
       </c>
       <c r="F35">
-        <v>62.7</v>
+        <v>64.60000000000001</v>
       </c>
       <c r="G35">
         <v>11.7</v>
@@ -4157,28 +4157,28 @@
         <v>10.8</v>
       </c>
       <c r="M35">
-        <v>4.752660000000001</v>
+        <v>4.896680000000001</v>
       </c>
       <c r="N35">
-        <v>6.04734</v>
+        <v>5.90332</v>
       </c>
       <c r="O35">
-        <v>1.511835</v>
+        <v>1.47583</v>
       </c>
       <c r="P35">
-        <v>4.535505000000001</v>
+        <v>4.42749</v>
       </c>
       <c r="Q35">
-        <v>16.235505</v>
+        <v>16.12749</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1378764250491092</v>
+        <v>0.1390168316016124</v>
       </c>
       <c r="T35">
-        <v>1.424393011697479</v>
+        <v>1.442034738371959</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.272411659996718</v>
+        <v>2.20557602293799</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1110801088570642</v>
+        <v>0.1110225129312252</v>
       </c>
       <c r="C36">
-        <v>126.5005597042684</v>
+        <v>124.6949869326258</v>
       </c>
       <c r="D36">
-        <v>179.4005597042684</v>
+        <v>179.4949869326258</v>
       </c>
       <c r="E36">
-        <v>44.10000000000001</v>
+        <v>46</v>
       </c>
       <c r="F36">
-        <v>64.60000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="G36">
         <v>11.7</v>
@@ -4239,28 +4239,28 @@
         <v>10.8</v>
       </c>
       <c r="M36">
-        <v>4.896680000000001</v>
+        <v>5.0407</v>
       </c>
       <c r="N36">
-        <v>5.90332</v>
+        <v>5.759300000000001</v>
       </c>
       <c r="O36">
-        <v>1.47583</v>
+        <v>1.439825</v>
       </c>
       <c r="P36">
-        <v>4.42749</v>
+        <v>4.319475000000001</v>
       </c>
       <c r="Q36">
-        <v>16.12749</v>
+        <v>16.019475</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1390168316016124</v>
+        <v>0.1401923275865004</v>
       </c>
       <c r="T36">
-        <v>1.442034738371959</v>
+        <v>1.460219287405653</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.20557602293799</v>
+        <v>2.142559565139762</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1110225129312252</v>
+        <v>0.1109649170053863</v>
       </c>
       <c r="C37">
-        <v>124.6949869326258</v>
+        <v>122.8895136166051</v>
       </c>
       <c r="D37">
-        <v>179.4949869326258</v>
+        <v>179.5895136166051</v>
       </c>
       <c r="E37">
-        <v>46</v>
+        <v>47.90000000000001</v>
       </c>
       <c r="F37">
-        <v>66.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G37">
         <v>11.7</v>
@@ -4321,28 +4321,28 @@
         <v>10.8</v>
       </c>
       <c r="M37">
-        <v>5.0407</v>
+        <v>5.18472</v>
       </c>
       <c r="N37">
-        <v>5.759300000000001</v>
+        <v>5.61528</v>
       </c>
       <c r="O37">
-        <v>1.439825</v>
+        <v>1.40382</v>
       </c>
       <c r="P37">
-        <v>4.319475000000001</v>
+        <v>4.211460000000001</v>
       </c>
       <c r="Q37">
-        <v>16.019475</v>
+        <v>15.91146</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1401923275865004</v>
+        <v>0.141404557820916</v>
       </c>
       <c r="T37">
-        <v>1.460219287405653</v>
+        <v>1.47897210359665</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.142559565139762</v>
+        <v>2.083044021663658</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1109649170053863</v>
+        <v>0.1109073210795473</v>
       </c>
       <c r="C38">
-        <v>122.8895136166051</v>
+        <v>121.0841399134167</v>
       </c>
       <c r="D38">
-        <v>179.5895136166051</v>
+        <v>179.6841399134167</v>
       </c>
       <c r="E38">
-        <v>47.89999999999999</v>
+        <v>49.8</v>
       </c>
       <c r="F38">
-        <v>68.39999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="G38">
         <v>11.7</v>
@@ -4403,28 +4403,28 @@
         <v>10.8</v>
       </c>
       <c r="M38">
-        <v>5.18472</v>
+        <v>5.32874</v>
       </c>
       <c r="N38">
-        <v>5.615280000000001</v>
+        <v>5.471260000000001</v>
       </c>
       <c r="O38">
-        <v>1.40382</v>
+        <v>1.367815</v>
       </c>
       <c r="P38">
-        <v>4.211460000000001</v>
+        <v>4.103445000000001</v>
       </c>
       <c r="Q38">
-        <v>15.91146</v>
+        <v>15.803445</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.141404557820916</v>
+        <v>0.142655271554837</v>
       </c>
       <c r="T38">
-        <v>1.47897210359665</v>
+        <v>1.498320247285774</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.083044021663658</v>
+        <v>2.026745534591667</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1109073210795473</v>
+        <v>0.1148967251537083</v>
       </c>
       <c r="C39">
-        <v>121.0841399134167</v>
+        <v>112.8572659623537</v>
       </c>
       <c r="D39">
-        <v>179.6841399134167</v>
+        <v>173.3572659623537</v>
       </c>
       <c r="E39">
-        <v>49.8</v>
+        <v>51.7</v>
       </c>
       <c r="F39">
-        <v>70.3</v>
+        <v>72.2</v>
       </c>
       <c r="G39">
         <v>11.7</v>
@@ -4485,45 +4485,45 @@
         <v>10.8</v>
       </c>
       <c r="M39">
-        <v>5.32874</v>
+        <v>6.498</v>
       </c>
       <c r="N39">
-        <v>5.471260000000001</v>
+        <v>4.302</v>
       </c>
       <c r="O39">
-        <v>1.367815</v>
+        <v>1.0755</v>
       </c>
       <c r="P39">
-        <v>4.103445000000001</v>
+        <v>3.226500000000001</v>
       </c>
       <c r="Q39">
-        <v>15.803445</v>
+        <v>14.9265</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.142655271554837</v>
+        <v>0.1439463308930779</v>
       </c>
       <c r="T39">
-        <v>1.498320247285774</v>
+        <v>1.518292524642289</v>
       </c>
       <c r="U39">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.026745534591667</v>
+        <v>1.662049861495845</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1148967251537083</v>
+        <v>0.1149456292278693</v>
       </c>
       <c r="C40">
-        <v>112.8572659623537</v>
+        <v>110.8824712175987</v>
       </c>
       <c r="D40">
-        <v>173.3572659623537</v>
+        <v>173.2824712175987</v>
       </c>
       <c r="E40">
-        <v>51.7</v>
+        <v>53.60000000000001</v>
       </c>
       <c r="F40">
-        <v>72.2</v>
+        <v>74.10000000000001</v>
       </c>
       <c r="G40">
         <v>11.7</v>
@@ -4567,28 +4567,28 @@
         <v>10.8</v>
       </c>
       <c r="M40">
-        <v>6.498</v>
+        <v>6.669</v>
       </c>
       <c r="N40">
-        <v>4.302</v>
+        <v>4.131</v>
       </c>
       <c r="O40">
-        <v>1.0755</v>
+        <v>1.03275</v>
       </c>
       <c r="P40">
-        <v>3.226500000000001</v>
+        <v>3.09825</v>
       </c>
       <c r="Q40">
-        <v>14.9265</v>
+        <v>14.79825</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1439463308930779</v>
+        <v>0.1452797200456875</v>
       </c>
       <c r="T40">
-        <v>1.518292524642289</v>
+        <v>1.538919630764592</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.662049861495845</v>
+        <v>1.619433198380567</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1149456292278693</v>
+        <v>0.1149945333020304</v>
       </c>
       <c r="C41">
-        <v>110.8824712175987</v>
+        <v>108.9077409851816</v>
       </c>
       <c r="D41">
-        <v>173.2824712175987</v>
+        <v>173.2077409851816</v>
       </c>
       <c r="E41">
-        <v>53.60000000000001</v>
+        <v>55.5</v>
       </c>
       <c r="F41">
-        <v>74.10000000000001</v>
+        <v>76</v>
       </c>
       <c r="G41">
         <v>11.7</v>
@@ -4649,28 +4649,28 @@
         <v>10.8</v>
       </c>
       <c r="M41">
-        <v>6.669</v>
+        <v>6.84</v>
       </c>
       <c r="N41">
-        <v>4.131</v>
+        <v>3.960000000000001</v>
       </c>
       <c r="O41">
-        <v>1.03275</v>
+        <v>0.9900000000000002</v>
       </c>
       <c r="P41">
-        <v>3.09825</v>
+        <v>2.970000000000001</v>
       </c>
       <c r="Q41">
-        <v>14.79825</v>
+        <v>14.67</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1452797200456875</v>
+        <v>0.1466575555033839</v>
       </c>
       <c r="T41">
-        <v>1.538919630764592</v>
+        <v>1.560234307090971</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.619433198380567</v>
+        <v>1.578947368421053</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1149945333020304</v>
+        <v>0.1150434373761914</v>
       </c>
       <c r="C42">
-        <v>108.9077409851816</v>
+        <v>106.9330751816729</v>
       </c>
       <c r="D42">
-        <v>173.2077409851816</v>
+        <v>173.1330751816729</v>
       </c>
       <c r="E42">
-        <v>55.5</v>
+        <v>57.40000000000001</v>
       </c>
       <c r="F42">
-        <v>76</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="G42">
         <v>11.7</v>
@@ -4731,28 +4731,28 @@
         <v>10.8</v>
       </c>
       <c r="M42">
-        <v>6.84</v>
+        <v>7.011</v>
       </c>
       <c r="N42">
-        <v>3.960000000000001</v>
+        <v>3.789000000000001</v>
       </c>
       <c r="O42">
-        <v>0.9900000000000002</v>
+        <v>0.9472500000000001</v>
       </c>
       <c r="P42">
-        <v>2.970000000000001</v>
+        <v>2.84175</v>
       </c>
       <c r="Q42">
-        <v>14.67</v>
+        <v>14.54175</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1466575555033839</v>
+        <v>0.148082097247782</v>
       </c>
       <c r="T42">
-        <v>1.560234307090971</v>
+        <v>1.582271514818245</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.578947368421053</v>
+        <v>1.540436456996149</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1150434373761914</v>
+        <v>0.1150923414503524</v>
       </c>
       <c r="C43">
-        <v>106.9330751816729</v>
+        <v>104.9584737237873</v>
       </c>
       <c r="D43">
-        <v>173.1330751816729</v>
+        <v>173.0584737237873</v>
       </c>
       <c r="E43">
-        <v>57.40000000000001</v>
+        <v>59.30000000000001</v>
       </c>
       <c r="F43">
-        <v>77.90000000000001</v>
+        <v>79.80000000000001</v>
       </c>
       <c r="G43">
         <v>11.7</v>
@@ -4813,28 +4813,28 @@
         <v>10.8</v>
       </c>
       <c r="M43">
-        <v>7.011</v>
+        <v>7.182</v>
       </c>
       <c r="N43">
-        <v>3.789000000000001</v>
+        <v>3.618</v>
       </c>
       <c r="O43">
-        <v>0.9472500000000001</v>
+        <v>0.9045000000000001</v>
       </c>
       <c r="P43">
-        <v>2.84175</v>
+        <v>2.7135</v>
       </c>
       <c r="Q43">
-        <v>14.54175</v>
+        <v>14.4135</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.148082097247782</v>
+        <v>0.1495557611212973</v>
       </c>
       <c r="T43">
-        <v>1.582271514818245</v>
+        <v>1.605068626260252</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.540436456996149</v>
+        <v>1.503759398496241</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1150923414503524</v>
+        <v>0.1357490386309396</v>
       </c>
       <c r="C44">
-        <v>104.9584737237873</v>
+        <v>76.41095963813201</v>
       </c>
       <c r="D44">
-        <v>173.0584737237873</v>
+        <v>146.410959638132</v>
       </c>
       <c r="E44">
-        <v>59.3</v>
+        <v>61.2</v>
       </c>
       <c r="F44">
-        <v>79.8</v>
+        <v>81.7</v>
       </c>
       <c r="G44">
         <v>11.7</v>
@@ -4895,45 +4895,45 @@
         <v>10.8</v>
       </c>
       <c r="M44">
-        <v>7.181999999999999</v>
+        <v>11.99356</v>
       </c>
       <c r="N44">
-        <v>3.618000000000001</v>
+        <v>-1.193560000000002</v>
       </c>
       <c r="O44">
-        <v>0.9045000000000003</v>
+        <v>-0.2983900000000004</v>
       </c>
       <c r="P44">
-        <v>2.713500000000001</v>
+        <v>-0.8951700000000011</v>
       </c>
       <c r="Q44">
-        <v>14.4135</v>
+        <v>10.80483</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1495557611212973</v>
+        <v>0.1523430963977702</v>
       </c>
       <c r="T44">
-        <v>1.605068626260252</v>
+        <v>1.648187816508444</v>
       </c>
       <c r="U44">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.25</v>
+        <v>0.225120814837296</v>
       </c>
       <c r="W44">
-        <v>0.0675</v>
+        <v>0.113752264381885</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y44">
-        <v>1.503759398496241</v>
+        <v>0.9004832593491839</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1357490386309396</v>
+        <v>0.1367590386309396</v>
       </c>
       <c r="C45">
-        <v>76.41095963813201</v>
+        <v>73.41690137442308</v>
       </c>
       <c r="D45">
-        <v>146.410959638132</v>
+        <v>145.3169013744231</v>
       </c>
       <c r="E45">
-        <v>61.2</v>
+        <v>63.09999999999999</v>
       </c>
       <c r="F45">
-        <v>81.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G45">
         <v>11.7</v>
@@ -4977,37 +4977,37 @@
         <v>10.8</v>
       </c>
       <c r="M45">
-        <v>11.99356</v>
+        <v>12.27248</v>
       </c>
       <c r="N45">
-        <v>-1.193560000000002</v>
+        <v>-1.472479999999999</v>
       </c>
       <c r="O45">
-        <v>-0.2983900000000004</v>
+        <v>-0.3681199999999998</v>
       </c>
       <c r="P45">
-        <v>-0.8951700000000011</v>
+        <v>-1.104359999999999</v>
       </c>
       <c r="Q45">
-        <v>10.80483</v>
+        <v>10.59564</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1523430963977702</v>
+        <v>0.1542456516905875</v>
       </c>
       <c r="T45">
-        <v>1.648187816508444</v>
+        <v>1.677619741803237</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.225120814837296</v>
+        <v>0.220004432681903</v>
       </c>
       <c r="W45">
-        <v>0.113752264381885</v>
+        <v>0.1145033492822967</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.9004832593491839</v>
+        <v>0.8800177307276118</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1367590386309396</v>
+        <v>0.1377690386309395</v>
       </c>
       <c r="C46">
-        <v>73.41690137442308</v>
+        <v>70.43907257194087</v>
       </c>
       <c r="D46">
-        <v>145.3169013744231</v>
+        <v>144.2390725719409</v>
       </c>
       <c r="E46">
-        <v>63.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="F46">
-        <v>83.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="G46">
         <v>11.7</v>
@@ -5059,37 +5059,37 @@
         <v>10.8</v>
       </c>
       <c r="M46">
-        <v>12.27248</v>
+        <v>12.5514</v>
       </c>
       <c r="N46">
-        <v>-1.472479999999999</v>
+        <v>-1.7514</v>
       </c>
       <c r="O46">
-        <v>-0.3681199999999998</v>
+        <v>-0.4378500000000001</v>
       </c>
       <c r="P46">
-        <v>-1.104359999999999</v>
+        <v>-1.31355</v>
       </c>
       <c r="Q46">
-        <v>10.59564</v>
+        <v>10.38645</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1542456516905875</v>
+        <v>0.1562173908122345</v>
       </c>
       <c r="T46">
-        <v>1.677619741803237</v>
+        <v>1.708121918926932</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.220004432681903</v>
+        <v>0.2151154452889718</v>
       </c>
       <c r="W46">
-        <v>0.1145033492822967</v>
+        <v>0.115221052631579</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8800177307276118</v>
+        <v>0.860461781155887</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1377690386309395</v>
+        <v>0.1387790386309395</v>
       </c>
       <c r="C47">
-        <v>70.43907257194087</v>
+        <v>67.47711476325813</v>
       </c>
       <c r="D47">
-        <v>144.2390725719409</v>
+        <v>143.1771147632581</v>
       </c>
       <c r="E47">
-        <v>65</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F47">
-        <v>85.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="G47">
         <v>11.7</v>
@@ -5141,37 +5141,37 @@
         <v>10.8</v>
       </c>
       <c r="M47">
-        <v>12.5514</v>
+        <v>12.83032</v>
       </c>
       <c r="N47">
-        <v>-1.7514</v>
+        <v>-2.030320000000001</v>
       </c>
       <c r="O47">
-        <v>-0.4378500000000001</v>
+        <v>-0.5075800000000004</v>
       </c>
       <c r="P47">
-        <v>-1.31355</v>
+        <v>-1.522740000000001</v>
       </c>
       <c r="Q47">
-        <v>10.38645</v>
+        <v>10.17726</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1562173908122345</v>
+        <v>0.1582621573087574</v>
       </c>
       <c r="T47">
-        <v>1.708121918926932</v>
+        <v>1.739753806314468</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2151154452889718</v>
+        <v>0.2104390225652984</v>
       </c>
       <c r="W47">
-        <v>0.115221052631579</v>
+        <v>0.1159075514874142</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.860461781155887</v>
+        <v>0.8417560902611937</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1387790386309395</v>
+        <v>0.1397890386309396</v>
       </c>
       <c r="C48">
-        <v>67.47711476325813</v>
+        <v>64.53067996063348</v>
       </c>
       <c r="D48">
-        <v>143.1771147632581</v>
+        <v>142.1306799606335</v>
       </c>
       <c r="E48">
-        <v>66.90000000000001</v>
+        <v>68.80000000000001</v>
       </c>
       <c r="F48">
-        <v>87.40000000000001</v>
+        <v>89.30000000000001</v>
       </c>
       <c r="G48">
         <v>11.7</v>
@@ -5223,37 +5223,37 @@
         <v>10.8</v>
       </c>
       <c r="M48">
-        <v>12.83032</v>
+        <v>13.10924</v>
       </c>
       <c r="N48">
-        <v>-2.030320000000001</v>
+        <v>-2.309240000000003</v>
       </c>
       <c r="O48">
-        <v>-0.5075800000000004</v>
+        <v>-0.5773100000000007</v>
       </c>
       <c r="P48">
-        <v>-1.522740000000001</v>
+        <v>-1.731930000000002</v>
       </c>
       <c r="Q48">
-        <v>10.17726</v>
+        <v>9.968069999999997</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1582621573087574</v>
+        <v>0.1603840848051491</v>
       </c>
       <c r="T48">
-        <v>1.739753806314468</v>
+        <v>1.772579349829836</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2104390225652984</v>
+        <v>0.2059615965532708</v>
       </c>
       <c r="W48">
-        <v>0.1159075514874142</v>
+        <v>0.1165648376259799</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8417560902611937</v>
+        <v>0.8238463862130831</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1397890386309396</v>
+        <v>0.1407990386309396</v>
       </c>
       <c r="C49">
-        <v>64.53067996063348</v>
+        <v>61.59943027582686</v>
       </c>
       <c r="D49">
-        <v>142.1306799606335</v>
+        <v>141.0994302758269</v>
       </c>
       <c r="E49">
-        <v>68.80000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="F49">
-        <v>89.30000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="G49">
         <v>11.7</v>
@@ -5305,37 +5305,37 @@
         <v>10.8</v>
       </c>
       <c r="M49">
-        <v>13.10924</v>
+        <v>13.38816</v>
       </c>
       <c r="N49">
-        <v>-2.309240000000003</v>
+        <v>-2.58816</v>
       </c>
       <c r="O49">
-        <v>-0.5773100000000007</v>
+        <v>-0.6470400000000001</v>
       </c>
       <c r="P49">
-        <v>-1.731930000000002</v>
+        <v>-1.94112</v>
       </c>
       <c r="Q49">
-        <v>9.968069999999997</v>
+        <v>9.75888</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1603840848051491</v>
+        <v>0.1625876248975558</v>
       </c>
       <c r="T49">
-        <v>1.772579349829836</v>
+        <v>1.80666741424964</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2059615965532708</v>
+        <v>0.201670729958411</v>
       </c>
       <c r="W49">
-        <v>0.1165648376259799</v>
+        <v>0.1171947368421053</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8238463862130831</v>
+        <v>0.806682919833644</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1407990386309395</v>
+        <v>0.170019414582127</v>
       </c>
       <c r="C50">
-        <v>61.59943027582686</v>
+        <v>35.21943388418609</v>
       </c>
       <c r="D50">
-        <v>141.0994302758269</v>
+        <v>116.6194338841861</v>
       </c>
       <c r="E50">
-        <v>70.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F50">
-        <v>91.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G50">
         <v>11.7</v>
@@ -5387,45 +5387,45 @@
         <v>10.8</v>
       </c>
       <c r="M50">
-        <v>13.38816</v>
+        <v>18.69448</v>
       </c>
       <c r="N50">
-        <v>-2.58816</v>
+        <v>-7.894479999999998</v>
       </c>
       <c r="O50">
-        <v>-0.6470400000000001</v>
+        <v>-1.973619999999999</v>
       </c>
       <c r="P50">
-        <v>-1.94112</v>
+        <v>-5.920859999999998</v>
       </c>
       <c r="Q50">
-        <v>9.75888</v>
+        <v>5.779140000000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1625876248975558</v>
+        <v>0.1683096880351305</v>
       </c>
       <c r="T50">
-        <v>1.80666741424964</v>
+        <v>1.895185911153772</v>
       </c>
       <c r="U50">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.201670729958411</v>
+        <v>0.1444276599295621</v>
       </c>
       <c r="W50">
-        <v>0.1171947368421053</v>
+        <v>0.1717989258861439</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.806682919833644</v>
+        <v>0.5777106397182485</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.170019414582127</v>
+        <v>0.1715694145821271</v>
       </c>
       <c r="C51">
-        <v>35.21943388418609</v>
+        <v>32.25596604496428</v>
       </c>
       <c r="D51">
-        <v>116.6194338841861</v>
+        <v>115.5559660449643</v>
       </c>
       <c r="E51">
-        <v>72.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="F51">
-        <v>93.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="G51">
         <v>11.7</v>
@@ -5469,37 +5469,37 @@
         <v>10.8</v>
       </c>
       <c r="M51">
-        <v>18.69448</v>
+        <v>19.076</v>
       </c>
       <c r="N51">
-        <v>-7.894479999999998</v>
+        <v>-8.276</v>
       </c>
       <c r="O51">
-        <v>-1.973619999999999</v>
+        <v>-2.069</v>
       </c>
       <c r="P51">
-        <v>-5.920859999999998</v>
+        <v>-6.207</v>
       </c>
       <c r="Q51">
-        <v>5.779140000000001</v>
+        <v>5.492999999999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1683096880351305</v>
+        <v>0.1707598817958331</v>
       </c>
       <c r="T51">
-        <v>1.895185911153772</v>
+        <v>1.933089629376848</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1444276599295621</v>
+        <v>0.1415391067309709</v>
       </c>
       <c r="W51">
-        <v>0.1717989258861439</v>
+        <v>0.1723789473684211</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5777106397182485</v>
+        <v>0.5661564269238835</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1715694145821271</v>
+        <v>0.1731194145821271</v>
       </c>
       <c r="C52">
-        <v>32.25596604496428</v>
+        <v>29.31171873529263</v>
       </c>
       <c r="D52">
-        <v>115.5559660449643</v>
+        <v>114.5117187352926</v>
       </c>
       <c r="E52">
-        <v>74.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F52">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G52">
         <v>11.7</v>
@@ -5551,37 +5551,37 @@
         <v>10.8</v>
       </c>
       <c r="M52">
-        <v>19.076</v>
+        <v>19.45752</v>
       </c>
       <c r="N52">
-        <v>-8.276</v>
+        <v>-8.657520000000002</v>
       </c>
       <c r="O52">
-        <v>-2.069</v>
+        <v>-2.16438</v>
       </c>
       <c r="P52">
-        <v>-6.207</v>
+        <v>-6.493140000000001</v>
       </c>
       <c r="Q52">
-        <v>5.492999999999999</v>
+        <v>5.206859999999998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1707598817958331</v>
+        <v>0.1733100834651358</v>
       </c>
       <c r="T52">
-        <v>1.933089629376848</v>
+        <v>1.972540438139641</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1415391067309709</v>
+        <v>0.1387638301284028</v>
       </c>
       <c r="W52">
-        <v>0.1723789473684211</v>
+        <v>0.1729362229102167</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5661564269238835</v>
+        <v>0.5550553205136112</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1731194145821271</v>
+        <v>0.1746694145821271</v>
       </c>
       <c r="C53">
-        <v>29.31171873529263</v>
+        <v>26.3861755499512</v>
       </c>
       <c r="D53">
-        <v>114.5117187352926</v>
+        <v>113.4861755499512</v>
       </c>
       <c r="E53">
-        <v>76.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="F53">
-        <v>96.90000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="G53">
         <v>11.7</v>
@@ -5633,37 +5633,37 @@
         <v>10.8</v>
       </c>
       <c r="M53">
-        <v>19.45752</v>
+        <v>19.83904</v>
       </c>
       <c r="N53">
-        <v>-8.657520000000002</v>
+        <v>-9.03904</v>
       </c>
       <c r="O53">
-        <v>-2.16438</v>
+        <v>-2.25976</v>
       </c>
       <c r="P53">
-        <v>-6.493140000000001</v>
+        <v>-6.77928</v>
       </c>
       <c r="Q53">
-        <v>5.206859999999998</v>
+        <v>4.920719999999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1733100834651358</v>
+        <v>0.1759665435373261</v>
       </c>
       <c r="T53">
-        <v>1.972540438139641</v>
+        <v>2.013635030600883</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1387638301284028</v>
+        <v>0.1360952949336258</v>
       </c>
       <c r="W53">
-        <v>0.1729362229102167</v>
+        <v>0.1734720647773279</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5550553205136112</v>
+        <v>0.5443811797345033</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1746694145821271</v>
+        <v>0.1762194145821271</v>
       </c>
       <c r="C54">
-        <v>26.3861755499512</v>
+        <v>23.47883841878682</v>
       </c>
       <c r="D54">
-        <v>113.4861755499512</v>
+        <v>112.4788384187868</v>
       </c>
       <c r="E54">
-        <v>78.3</v>
+        <v>80.2</v>
       </c>
       <c r="F54">
-        <v>98.8</v>
+        <v>100.7</v>
       </c>
       <c r="G54">
         <v>11.7</v>
@@ -5715,37 +5715,37 @@
         <v>10.8</v>
       </c>
       <c r="M54">
-        <v>19.83904</v>
+        <v>20.22056</v>
       </c>
       <c r="N54">
-        <v>-9.03904</v>
+        <v>-9.420560000000002</v>
       </c>
       <c r="O54">
-        <v>-2.25976</v>
+        <v>-2.35514</v>
       </c>
       <c r="P54">
-        <v>-6.77928</v>
+        <v>-7.065420000000001</v>
       </c>
       <c r="Q54">
-        <v>4.920719999999999</v>
+        <v>4.634579999999998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1759665435373261</v>
+        <v>0.1787360444636522</v>
       </c>
       <c r="T54">
-        <v>2.013635030600883</v>
+        <v>2.056478329124306</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1360952949336258</v>
+        <v>0.1335274591801612</v>
       </c>
       <c r="W54">
-        <v>0.1734720647773279</v>
+        <v>0.1739876861966236</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5443811797345033</v>
+        <v>0.5341098367206447</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1762194145821271</v>
+        <v>0.1777694145821271</v>
       </c>
       <c r="C55">
-        <v>23.47883841878682</v>
+        <v>20.58922680013511</v>
       </c>
       <c r="D55">
-        <v>112.4788384187868</v>
+        <v>111.4892268001351</v>
       </c>
       <c r="E55">
-        <v>80.2</v>
+        <v>82.10000000000001</v>
       </c>
       <c r="F55">
-        <v>100.7</v>
+        <v>102.6</v>
       </c>
       <c r="G55">
         <v>11.7</v>
@@ -5797,37 +5797,37 @@
         <v>10.8</v>
       </c>
       <c r="M55">
-        <v>20.22056</v>
+        <v>20.60208</v>
       </c>
       <c r="N55">
-        <v>-9.420560000000002</v>
+        <v>-9.80208</v>
       </c>
       <c r="O55">
-        <v>-2.35514</v>
+        <v>-2.45052</v>
       </c>
       <c r="P55">
-        <v>-7.065420000000001</v>
+        <v>-7.35156</v>
       </c>
       <c r="Q55">
-        <v>4.634579999999998</v>
+        <v>4.348439999999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1787360444636522</v>
+        <v>0.1816259584737316</v>
       </c>
       <c r="T55">
-        <v>2.056478329124306</v>
+        <v>2.101184379757443</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1335274591801612</v>
+        <v>0.1310547284546026</v>
       </c>
       <c r="W55">
-        <v>0.1739876861966236</v>
+        <v>0.1744842105263158</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5341098367206447</v>
+        <v>0.5242189138184106</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1777694145821271</v>
+        <v>0.1793194145821271</v>
       </c>
       <c r="C56">
-        <v>20.58922680013511</v>
+        <v>17.71687691644932</v>
       </c>
       <c r="D56">
-        <v>111.4892268001351</v>
+        <v>110.5168769164493</v>
       </c>
       <c r="E56">
-        <v>82.10000000000001</v>
+        <v>84.00000000000001</v>
       </c>
       <c r="F56">
-        <v>102.6</v>
+        <v>104.5</v>
       </c>
       <c r="G56">
         <v>11.7</v>
@@ -5879,37 +5879,37 @@
         <v>10.8</v>
       </c>
       <c r="M56">
-        <v>20.60208</v>
+        <v>20.9836</v>
       </c>
       <c r="N56">
-        <v>-9.80208</v>
+        <v>-10.1836</v>
       </c>
       <c r="O56">
-        <v>-2.45052</v>
+        <v>-2.5459</v>
       </c>
       <c r="P56">
-        <v>-7.35156</v>
+        <v>-7.637700000000001</v>
       </c>
       <c r="Q56">
-        <v>4.348439999999999</v>
+        <v>4.062299999999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1816259584737316</v>
+        <v>0.1846443131064812</v>
       </c>
       <c r="T56">
-        <v>2.101184379757443</v>
+        <v>2.147877365974275</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1310547284546026</v>
+        <v>0.1286719152099735</v>
       </c>
       <c r="W56">
-        <v>0.1744842105263158</v>
+        <v>0.1749626794258373</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5242189138184106</v>
+        <v>0.514687660839894</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1793194145821271</v>
+        <v>0.1808694145821271</v>
       </c>
       <c r="C57">
-        <v>17.71687691644932</v>
+        <v>14.86134102958242</v>
       </c>
       <c r="D57">
-        <v>110.5168769164493</v>
+        <v>109.5613410295824</v>
       </c>
       <c r="E57">
-        <v>84.00000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F57">
-        <v>104.5</v>
+        <v>106.4</v>
       </c>
       <c r="G57">
         <v>11.7</v>
@@ -5961,37 +5961,37 @@
         <v>10.8</v>
       </c>
       <c r="M57">
-        <v>20.9836</v>
+        <v>21.36512</v>
       </c>
       <c r="N57">
-        <v>-10.1836</v>
+        <v>-10.56512</v>
       </c>
       <c r="O57">
-        <v>-2.5459</v>
+        <v>-2.64128</v>
       </c>
       <c r="P57">
-        <v>-7.637700000000001</v>
+        <v>-7.92384</v>
       </c>
       <c r="Q57">
-        <v>4.062299999999998</v>
+        <v>3.776159999999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1846443131064812</v>
+        <v>0.1877998656770831</v>
       </c>
       <c r="T57">
-        <v>2.147877365974275</v>
+        <v>2.196692760655509</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1286719152099735</v>
+        <v>0.1263742024383668</v>
       </c>
       <c r="W57">
-        <v>0.1749626794258373</v>
+        <v>0.175424060150376</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.514687660839894</v>
+        <v>0.5054968097534673</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1808694145821271</v>
+        <v>0.2030757124206281</v>
       </c>
       <c r="C58">
-        <v>14.86134102958242</v>
+        <v>0.8858588068629558</v>
       </c>
       <c r="D58">
-        <v>109.5613410295824</v>
+        <v>97.48585880686296</v>
       </c>
       <c r="E58">
-        <v>85.90000000000001</v>
+        <v>87.80000000000001</v>
       </c>
       <c r="F58">
-        <v>106.4</v>
+        <v>108.3</v>
       </c>
       <c r="G58">
         <v>11.7</v>
@@ -6043,45 +6043,45 @@
         <v>10.8</v>
       </c>
       <c r="M58">
-        <v>21.36512</v>
+        <v>25.53714</v>
       </c>
       <c r="N58">
-        <v>-10.56512</v>
+        <v>-14.73714</v>
       </c>
       <c r="O58">
-        <v>-2.64128</v>
+        <v>-3.684285000000001</v>
       </c>
       <c r="P58">
-        <v>-7.92384</v>
+        <v>-11.052855</v>
       </c>
       <c r="Q58">
-        <v>3.776159999999999</v>
+        <v>0.6471449999999965</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1877998656770831</v>
+        <v>0.1927447412474828</v>
       </c>
       <c r="T58">
-        <v>2.196692760655509</v>
+        <v>2.27318841307071</v>
       </c>
       <c r="U58">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1263742024383668</v>
+        <v>0.1057283626905754</v>
       </c>
       <c r="W58">
-        <v>0.175424060150376</v>
+        <v>0.2108692520775623</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.5054968097534673</v>
+        <v>0.4229134507623015</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2030757124206281</v>
+        <v>0.2049757124206281</v>
       </c>
       <c r="C59">
-        <v>0.8858588068629558</v>
+        <v>-1.924871686270819</v>
       </c>
       <c r="D59">
-        <v>97.48585880686296</v>
+        <v>96.57512831372919</v>
       </c>
       <c r="E59">
-        <v>87.80000000000001</v>
+        <v>89.70000000000002</v>
       </c>
       <c r="F59">
-        <v>108.3</v>
+        <v>110.2</v>
       </c>
       <c r="G59">
         <v>11.7</v>
@@ -6125,37 +6125,37 @@
         <v>10.8</v>
       </c>
       <c r="M59">
-        <v>25.53714</v>
+        <v>25.98516</v>
       </c>
       <c r="N59">
-        <v>-14.73714</v>
+        <v>-15.18516</v>
       </c>
       <c r="O59">
-        <v>-3.684285000000001</v>
+        <v>-3.796290000000001</v>
       </c>
       <c r="P59">
-        <v>-11.052855</v>
+        <v>-11.38887</v>
       </c>
       <c r="Q59">
-        <v>0.6471449999999965</v>
+        <v>0.3111299999999968</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1927447412474828</v>
+        <v>0.1962434255628991</v>
       </c>
       <c r="T59">
-        <v>2.27318841307071</v>
+        <v>2.327311946715251</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1057283626905754</v>
+        <v>0.1039054598855654</v>
       </c>
       <c r="W59">
-        <v>0.2108692520775623</v>
+        <v>0.2112990925589837</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4229134507623015</v>
+        <v>0.4156218395422617</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2049757124206281</v>
+        <v>0.2068757124206281</v>
       </c>
       <c r="C60">
-        <v>-1.924871686270777</v>
+        <v>-4.718743261081784</v>
       </c>
       <c r="D60">
-        <v>96.57512831372921</v>
+        <v>95.68125673891821</v>
       </c>
       <c r="E60">
-        <v>89.69999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F60">
-        <v>110.2</v>
+        <v>112.1</v>
       </c>
       <c r="G60">
         <v>11.7</v>
@@ -6207,37 +6207,37 @@
         <v>10.8</v>
       </c>
       <c r="M60">
-        <v>25.98516</v>
+        <v>26.43318</v>
       </c>
       <c r="N60">
-        <v>-15.18516</v>
+        <v>-15.63318</v>
       </c>
       <c r="O60">
-        <v>-3.796289999999999</v>
+        <v>-3.908295</v>
       </c>
       <c r="P60">
-        <v>-11.38887</v>
+        <v>-11.724885</v>
       </c>
       <c r="Q60">
-        <v>0.3111300000000021</v>
+        <v>-0.02488500000000116</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.196243425562899</v>
+        <v>0.1999127774058965</v>
       </c>
       <c r="T60">
-        <v>2.32731194671525</v>
+        <v>2.384075652732695</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1039054598855655</v>
+        <v>0.1021443503959796</v>
       </c>
       <c r="W60">
-        <v>0.2112990925589837</v>
+        <v>0.211714362176628</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4156218395422618</v>
+        <v>0.4085774015839184</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2068757124206281</v>
+        <v>0.2087757124206281</v>
       </c>
       <c r="C61">
-        <v>-4.718743261081784</v>
+        <v>-7.496219748364084</v>
       </c>
       <c r="D61">
-        <v>95.68125673891821</v>
+        <v>94.80378025163591</v>
       </c>
       <c r="E61">
-        <v>91.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="F61">
-        <v>112.1</v>
+        <v>114</v>
       </c>
       <c r="G61">
         <v>11.7</v>
@@ -6289,37 +6289,37 @@
         <v>10.8</v>
       </c>
       <c r="M61">
-        <v>26.43318</v>
+        <v>26.8812</v>
       </c>
       <c r="N61">
-        <v>-15.63318</v>
+        <v>-16.0812</v>
       </c>
       <c r="O61">
-        <v>-3.908295</v>
+        <v>-4.0203</v>
       </c>
       <c r="P61">
-        <v>-11.724885</v>
+        <v>-12.0609</v>
       </c>
       <c r="Q61">
-        <v>-0.02488500000000116</v>
+        <v>-0.3609000000000009</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1999127774058965</v>
+        <v>0.2037655968410439</v>
       </c>
       <c r="T61">
-        <v>2.384075652732695</v>
+        <v>2.443677544051012</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1021443503959796</v>
+        <v>0.1004419445560466</v>
       </c>
       <c r="W61">
-        <v>0.211714362176628</v>
+        <v>0.2121157894736842</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4085774015839184</v>
+        <v>0.4017677782241864</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2087757124206281</v>
+        <v>0.2106757124206281</v>
       </c>
       <c r="C62">
-        <v>-7.496219748364084</v>
+        <v>-10.2577481186815</v>
       </c>
       <c r="D62">
-        <v>94.80378025163591</v>
+        <v>93.94225188131848</v>
       </c>
       <c r="E62">
-        <v>93.5</v>
+        <v>95.39999999999999</v>
       </c>
       <c r="F62">
-        <v>114</v>
+        <v>115.9</v>
       </c>
       <c r="G62">
         <v>11.7</v>
@@ -6371,37 +6371,37 @@
         <v>10.8</v>
       </c>
       <c r="M62">
-        <v>26.8812</v>
+        <v>27.32922</v>
       </c>
       <c r="N62">
-        <v>-16.0812</v>
+        <v>-16.52922</v>
       </c>
       <c r="O62">
-        <v>-4.0203</v>
+        <v>-4.132305</v>
       </c>
       <c r="P62">
-        <v>-12.0609</v>
+        <v>-12.396915</v>
       </c>
       <c r="Q62">
-        <v>-0.3609000000000009</v>
+        <v>-0.6969150000000006</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2037655968410439</v>
+        <v>0.2078159967600451</v>
       </c>
       <c r="T62">
-        <v>2.443677544051012</v>
+        <v>2.506335942616423</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1004419445560466</v>
+        <v>0.09879535530102945</v>
       </c>
       <c r="W62">
-        <v>0.2121157894736842</v>
+        <v>0.2125040552200173</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4017677782241864</v>
+        <v>0.3951814212041178</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2106757124206281</v>
+        <v>0.2125757124206281</v>
       </c>
       <c r="C63">
-        <v>-10.2577481186815</v>
+        <v>-13.00375924155465</v>
       </c>
       <c r="D63">
-        <v>93.94225188131848</v>
+        <v>93.09624075844535</v>
       </c>
       <c r="E63">
-        <v>95.39999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="F63">
-        <v>115.9</v>
+        <v>117.8</v>
       </c>
       <c r="G63">
         <v>11.7</v>
@@ -6453,37 +6453,37 @@
         <v>10.8</v>
       </c>
       <c r="M63">
-        <v>27.32922</v>
+        <v>27.77724</v>
       </c>
       <c r="N63">
-        <v>-16.52922</v>
+        <v>-16.97724</v>
       </c>
       <c r="O63">
-        <v>-4.132305</v>
+        <v>-4.24431</v>
       </c>
       <c r="P63">
-        <v>-12.396915</v>
+        <v>-12.73293</v>
       </c>
       <c r="Q63">
-        <v>-0.6969150000000006</v>
+        <v>-1.03293</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2078159967600451</v>
+        <v>0.2120795756221516</v>
       </c>
       <c r="T63">
-        <v>2.506335942616423</v>
+        <v>2.572292151632645</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.09879535530102945</v>
+        <v>0.0972018818284322</v>
       </c>
       <c r="W63">
-        <v>0.2125040552200173</v>
+        <v>0.2128797962648557</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3951814212041178</v>
+        <v>0.3888075273137288</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2125757124206281</v>
+        <v>0.2144757124206281</v>
       </c>
       <c r="C64">
-        <v>-13.00375924155465</v>
+        <v>-15.73466860399161</v>
       </c>
       <c r="D64">
-        <v>93.09624075844535</v>
+        <v>92.26533139600839</v>
       </c>
       <c r="E64">
-        <v>97.3</v>
+        <v>99.2</v>
       </c>
       <c r="F64">
-        <v>117.8</v>
+        <v>119.7</v>
       </c>
       <c r="G64">
         <v>11.7</v>
@@ -6535,37 +6535,37 @@
         <v>10.8</v>
       </c>
       <c r="M64">
-        <v>27.77724</v>
+        <v>28.22526</v>
       </c>
       <c r="N64">
-        <v>-16.97724</v>
+        <v>-17.42526</v>
       </c>
       <c r="O64">
-        <v>-4.24431</v>
+        <v>-4.356315</v>
       </c>
       <c r="P64">
-        <v>-12.73293</v>
+        <v>-13.068945</v>
       </c>
       <c r="Q64">
-        <v>-1.03293</v>
+        <v>-1.368945000000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2120795756221516</v>
+        <v>0.216573618206534</v>
       </c>
       <c r="T64">
-        <v>2.572292151632645</v>
+        <v>2.64181356113623</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0972018818284322</v>
+        <v>0.09565899481528248</v>
       </c>
       <c r="W64">
-        <v>0.2128797962648557</v>
+        <v>0.2132436090225564</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3888075273137288</v>
+        <v>0.3826359792611299</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2144757124206281</v>
+        <v>0.2163757124206281</v>
       </c>
       <c r="C65">
-        <v>-15.73466860399161</v>
+        <v>-18.45087699088108</v>
       </c>
       <c r="D65">
-        <v>92.26533139600839</v>
+        <v>91.44912300911892</v>
       </c>
       <c r="E65">
-        <v>99.2</v>
+        <v>101.1</v>
       </c>
       <c r="F65">
-        <v>119.7</v>
+        <v>121.6</v>
       </c>
       <c r="G65">
         <v>11.7</v>
@@ -6617,37 +6617,37 @@
         <v>10.8</v>
       </c>
       <c r="M65">
-        <v>28.22526</v>
+        <v>28.67328</v>
       </c>
       <c r="N65">
-        <v>-17.42526</v>
+        <v>-17.87328</v>
       </c>
       <c r="O65">
-        <v>-4.356315</v>
+        <v>-4.46832</v>
       </c>
       <c r="P65">
-        <v>-13.068945</v>
+        <v>-13.40496</v>
       </c>
       <c r="Q65">
-        <v>-1.368945000000002</v>
+        <v>-1.704960000000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.216573618206534</v>
+        <v>0.2213173298233822</v>
       </c>
       <c r="T65">
-        <v>2.64181356113623</v>
+        <v>2.715197271167792</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.09565899481528248</v>
+        <v>0.0941643230212937</v>
       </c>
       <c r="W65">
-        <v>0.2132436090225564</v>
+        <v>0.2135960526315789</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3826359792611299</v>
+        <v>0.3766572920851747</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2163757124206281</v>
+        <v>0.2182757124206282</v>
       </c>
       <c r="C66">
-        <v>-18.45087699088108</v>
+        <v>-21.15277112958815</v>
       </c>
       <c r="D66">
-        <v>91.44912300911892</v>
+        <v>90.64722887041185</v>
       </c>
       <c r="E66">
-        <v>101.1</v>
+        <v>103</v>
       </c>
       <c r="F66">
-        <v>121.6</v>
+        <v>123.5</v>
       </c>
       <c r="G66">
         <v>11.7</v>
@@ -6699,37 +6699,37 @@
         <v>10.8</v>
       </c>
       <c r="M66">
-        <v>28.67328</v>
+        <v>29.1213</v>
       </c>
       <c r="N66">
-        <v>-17.87328</v>
+        <v>-18.3213</v>
       </c>
       <c r="O66">
-        <v>-4.46832</v>
+        <v>-4.580325</v>
       </c>
       <c r="P66">
-        <v>-13.40496</v>
+        <v>-13.740975</v>
       </c>
       <c r="Q66">
-        <v>-1.704960000000002</v>
+        <v>-2.040975000000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2213173298233822</v>
+        <v>0.2263321106754789</v>
       </c>
       <c r="T66">
-        <v>2.715197271167792</v>
+        <v>2.792774336058301</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0941643230212937</v>
+        <v>0.0927156411286584</v>
       </c>
       <c r="W66">
-        <v>0.2135960526315789</v>
+        <v>0.2139376518218624</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3766572920851747</v>
+        <v>0.3708625645146336</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2182757124206282</v>
+        <v>0.2201757124206281</v>
       </c>
       <c r="C67">
-        <v>-21.15277112958815</v>
+        <v>-23.84072430093082</v>
       </c>
       <c r="D67">
-        <v>90.64722887041185</v>
+        <v>89.85927569906919</v>
       </c>
       <c r="E67">
-        <v>103</v>
+        <v>104.9</v>
       </c>
       <c r="F67">
-        <v>123.5</v>
+        <v>125.4</v>
       </c>
       <c r="G67">
         <v>11.7</v>
@@ -6781,37 +6781,37 @@
         <v>10.8</v>
       </c>
       <c r="M67">
-        <v>29.1213</v>
+        <v>29.56932</v>
       </c>
       <c r="N67">
-        <v>-18.3213</v>
+        <v>-18.76932</v>
       </c>
       <c r="O67">
-        <v>-4.580325</v>
+        <v>-4.69233</v>
       </c>
       <c r="P67">
-        <v>-13.740975</v>
+        <v>-14.07699</v>
       </c>
       <c r="Q67">
-        <v>-2.040975000000001</v>
+        <v>-2.376990000000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2263321106754789</v>
+        <v>0.2316418786365223</v>
       </c>
       <c r="T67">
-        <v>2.792774336058301</v>
+        <v>2.874914757707074</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0927156411286584</v>
+        <v>0.0913108586873151</v>
       </c>
       <c r="W67">
-        <v>0.2139376518218624</v>
+        <v>0.2142688995215311</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3708625645146336</v>
+        <v>0.3652434347492604</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2201757124206281</v>
+        <v>0.2220757124206281</v>
       </c>
       <c r="C68">
-        <v>-23.84072430093082</v>
+        <v>-26.51509691856619</v>
       </c>
       <c r="D68">
-        <v>89.85927569906919</v>
+        <v>89.08490308143382</v>
       </c>
       <c r="E68">
-        <v>104.9</v>
+        <v>106.8</v>
       </c>
       <c r="F68">
-        <v>125.4</v>
+        <v>127.3</v>
       </c>
       <c r="G68">
         <v>11.7</v>
@@ -6863,37 +6863,37 @@
         <v>10.8</v>
       </c>
       <c r="M68">
-        <v>29.56932</v>
+        <v>30.01734</v>
       </c>
       <c r="N68">
-        <v>-18.76932</v>
+        <v>-19.21734</v>
       </c>
       <c r="O68">
-        <v>-4.69233</v>
+        <v>-4.804335000000001</v>
       </c>
       <c r="P68">
-        <v>-14.07699</v>
+        <v>-14.413005</v>
       </c>
       <c r="Q68">
-        <v>-2.376990000000001</v>
+        <v>-2.713005000000003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2316418786365223</v>
+        <v>0.237273450716417</v>
       </c>
       <c r="T68">
-        <v>2.874914757707074</v>
+        <v>2.9620333867285</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0913108586873151</v>
+        <v>0.08994801005019099</v>
       </c>
       <c r="W68">
-        <v>0.2142688995215311</v>
+        <v>0.2145902592301649</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3652434347492604</v>
+        <v>0.3597920402007639</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2220757124206281</v>
+        <v>0.2239757124206281</v>
       </c>
       <c r="C69">
-        <v>-26.51509691856619</v>
+        <v>-29.17623707867435</v>
       </c>
       <c r="D69">
-        <v>89.08490308143382</v>
+        <v>88.32376292132567</v>
       </c>
       <c r="E69">
-        <v>106.8</v>
+        <v>108.7</v>
       </c>
       <c r="F69">
-        <v>127.3</v>
+        <v>129.2</v>
       </c>
       <c r="G69">
         <v>11.7</v>
@@ -6945,37 +6945,37 @@
         <v>10.8</v>
       </c>
       <c r="M69">
-        <v>30.01734</v>
+        <v>30.46536</v>
       </c>
       <c r="N69">
-        <v>-19.21734</v>
+        <v>-19.66536</v>
       </c>
       <c r="O69">
-        <v>-4.804335000000001</v>
+        <v>-4.916340000000001</v>
       </c>
       <c r="P69">
-        <v>-14.413005</v>
+        <v>-14.74902</v>
       </c>
       <c r="Q69">
-        <v>-2.713005000000003</v>
+        <v>-3.049020000000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.237273450716417</v>
+        <v>0.243256996051305</v>
       </c>
       <c r="T69">
-        <v>2.9620333867285</v>
+        <v>3.054596930063767</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08994801005019099</v>
+        <v>0.0886252451965117</v>
       </c>
       <c r="W69">
-        <v>0.2145902592301649</v>
+        <v>0.2149021671826626</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3597920402007639</v>
+        <v>0.3545009807860469</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2239757124206281</v>
+        <v>0.2258757124206281</v>
       </c>
       <c r="C70">
-        <v>-29.17623707867435</v>
+        <v>-31.82448108170249</v>
       </c>
       <c r="D70">
-        <v>88.32376292132567</v>
+        <v>87.57551891829753</v>
       </c>
       <c r="E70">
-        <v>108.7</v>
+        <v>110.6</v>
       </c>
       <c r="F70">
-        <v>129.2</v>
+        <v>131.1</v>
       </c>
       <c r="G70">
         <v>11.7</v>
@@ -7027,37 +7027,37 @@
         <v>10.8</v>
       </c>
       <c r="M70">
-        <v>30.46536</v>
+        <v>30.91338000000001</v>
       </c>
       <c r="N70">
-        <v>-19.66536</v>
+        <v>-20.11338000000001</v>
       </c>
       <c r="O70">
-        <v>-4.916340000000001</v>
+        <v>-5.028345000000002</v>
       </c>
       <c r="P70">
-        <v>-14.74902</v>
+        <v>-15.085035</v>
       </c>
       <c r="Q70">
-        <v>-3.049020000000002</v>
+        <v>-3.385035000000006</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.243256996051305</v>
+        <v>0.249626576569089</v>
       </c>
       <c r="T70">
-        <v>3.054596930063767</v>
+        <v>3.153132314904533</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0886252451965117</v>
+        <v>0.08734082135308399</v>
       </c>
       <c r="W70">
-        <v>0.2149021671826626</v>
+        <v>0.2152050343249428</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3545009807860469</v>
+        <v>0.349363285412336</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2258757124206281</v>
+        <v>0.2277757124206281</v>
       </c>
       <c r="C71">
-        <v>-31.82448108170249</v>
+        <v>-34.46015392781163</v>
       </c>
       <c r="D71">
-        <v>87.57551891829753</v>
+        <v>86.83984607218837</v>
       </c>
       <c r="E71">
-        <v>110.6</v>
+        <v>112.5</v>
       </c>
       <c r="F71">
-        <v>131.1</v>
+        <v>133</v>
       </c>
       <c r="G71">
         <v>11.7</v>
@@ -7109,37 +7109,37 @@
         <v>10.8</v>
       </c>
       <c r="M71">
-        <v>30.91338000000001</v>
+        <v>31.3614</v>
       </c>
       <c r="N71">
-        <v>-20.11338000000001</v>
+        <v>-20.5614</v>
       </c>
       <c r="O71">
-        <v>-5.028345000000002</v>
+        <v>-5.14035</v>
       </c>
       <c r="P71">
-        <v>-15.085035</v>
+        <v>-15.42105</v>
       </c>
       <c r="Q71">
-        <v>-3.385035000000006</v>
+        <v>-3.72105</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.249626576569089</v>
+        <v>0.2564207957880587</v>
       </c>
       <c r="T71">
-        <v>3.153132314904533</v>
+        <v>3.258236725401351</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08734082135308399</v>
+        <v>0.08609309533375424</v>
       </c>
       <c r="W71">
-        <v>0.2152050343249428</v>
+        <v>0.2154992481203008</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.349363285412336</v>
+        <v>0.3443723813350169</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2277757124206281</v>
+        <v>0.2296757124206281</v>
       </c>
       <c r="C72">
-        <v>-34.46015392781163</v>
+        <v>-37.08356978755951</v>
       </c>
       <c r="D72">
-        <v>86.83984607218837</v>
+        <v>86.11643021244049</v>
       </c>
       <c r="E72">
-        <v>112.5</v>
+        <v>114.4</v>
       </c>
       <c r="F72">
-        <v>133</v>
+        <v>134.9</v>
       </c>
       <c r="G72">
         <v>11.7</v>
@@ -7191,37 +7191,37 @@
         <v>10.8</v>
       </c>
       <c r="M72">
-        <v>31.3614</v>
+        <v>31.80942</v>
       </c>
       <c r="N72">
-        <v>-20.5614</v>
+        <v>-21.00942</v>
       </c>
       <c r="O72">
-        <v>-5.14035</v>
+        <v>-5.252355000000001</v>
       </c>
       <c r="P72">
-        <v>-15.42105</v>
+        <v>-15.757065</v>
       </c>
       <c r="Q72">
-        <v>-3.72105</v>
+        <v>-4.057065000000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2564207957880587</v>
+        <v>0.2636835818497159</v>
       </c>
       <c r="T72">
-        <v>3.258236725401351</v>
+        <v>3.370589715932432</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08609309533375424</v>
+        <v>0.08488051652623657</v>
       </c>
       <c r="W72">
-        <v>0.2154992481203008</v>
+        <v>0.2157851742031134</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3443723813350169</v>
+        <v>0.3395220661049463</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2296757124206281</v>
+        <v>0.2315757124206281</v>
       </c>
       <c r="C73">
-        <v>-37.08356978755951</v>
+        <v>-39.69503244925176</v>
       </c>
       <c r="D73">
-        <v>86.11643021244049</v>
+        <v>85.40496755074822</v>
       </c>
       <c r="E73">
-        <v>114.4</v>
+        <v>116.3</v>
       </c>
       <c r="F73">
-        <v>134.9</v>
+        <v>136.8</v>
       </c>
       <c r="G73">
         <v>11.7</v>
@@ -7273,37 +7273,37 @@
         <v>10.8</v>
       </c>
       <c r="M73">
-        <v>31.80942</v>
+        <v>32.25744</v>
       </c>
       <c r="N73">
-        <v>-21.00942</v>
+        <v>-21.45743999999999</v>
       </c>
       <c r="O73">
-        <v>-5.252355000000001</v>
+        <v>-5.364359999999999</v>
       </c>
       <c r="P73">
-        <v>-15.757065</v>
+        <v>-16.09308</v>
       </c>
       <c r="Q73">
-        <v>-4.057065000000001</v>
+        <v>-4.393079999999998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2636835818497158</v>
+        <v>0.2714651383443485</v>
       </c>
       <c r="T73">
-        <v>3.370589715932431</v>
+        <v>3.490967920072875</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08488051652623657</v>
+        <v>0.08370162046337219</v>
       </c>
       <c r="W73">
-        <v>0.2157851742031134</v>
+        <v>0.2160631578947368</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3395220661049463</v>
+        <v>0.3348064818534887</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2315757124206281</v>
+        <v>0.2334757124206281</v>
       </c>
       <c r="C74">
-        <v>-39.69503244925176</v>
+        <v>-42.29483574429977</v>
       </c>
       <c r="D74">
-        <v>85.40496755074822</v>
+        <v>84.70516425570021</v>
       </c>
       <c r="E74">
-        <v>116.3</v>
+        <v>118.2</v>
       </c>
       <c r="F74">
-        <v>136.8</v>
+        <v>138.7</v>
       </c>
       <c r="G74">
         <v>11.7</v>
@@ -7355,37 +7355,37 @@
         <v>10.8</v>
       </c>
       <c r="M74">
-        <v>32.25744</v>
+        <v>32.70546</v>
       </c>
       <c r="N74">
-        <v>-21.45743999999999</v>
+        <v>-21.90546</v>
       </c>
       <c r="O74">
-        <v>-5.364359999999999</v>
+        <v>-5.476365</v>
       </c>
       <c r="P74">
-        <v>-16.09308</v>
+        <v>-16.429095</v>
       </c>
       <c r="Q74">
-        <v>-4.393079999999998</v>
+        <v>-4.729095000000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2714651383443485</v>
+        <v>0.2798231064311762</v>
       </c>
       <c r="T74">
-        <v>3.490967920072875</v>
+        <v>3.620263028223722</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08370162046337219</v>
+        <v>0.08255502292277803</v>
       </c>
       <c r="W74">
-        <v>0.2160631578947368</v>
+        <v>0.216333525594809</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3348064818534887</v>
+        <v>0.3302200916911121</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2334757124206281</v>
+        <v>0.2353757124206281</v>
       </c>
       <c r="C75">
-        <v>-42.29483574429977</v>
+        <v>-44.88326395183641</v>
       </c>
       <c r="D75">
-        <v>84.70516425570021</v>
+        <v>84.01673604816358</v>
       </c>
       <c r="E75">
-        <v>118.2</v>
+        <v>120.1</v>
       </c>
       <c r="F75">
-        <v>138.7</v>
+        <v>140.6</v>
       </c>
       <c r="G75">
         <v>11.7</v>
@@ -7437,37 +7437,37 @@
         <v>10.8</v>
       </c>
       <c r="M75">
-        <v>32.70546</v>
+        <v>33.15348</v>
       </c>
       <c r="N75">
-        <v>-21.90546</v>
+        <v>-22.35348</v>
       </c>
       <c r="O75">
-        <v>-5.476365</v>
+        <v>-5.58837</v>
       </c>
       <c r="P75">
-        <v>-16.429095</v>
+        <v>-16.76511</v>
       </c>
       <c r="Q75">
-        <v>-4.729095000000001</v>
+        <v>-5.065110000000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2798231064311762</v>
+        <v>0.2888239951400676</v>
       </c>
       <c r="T75">
-        <v>3.620263028223722</v>
+        <v>3.759503913924635</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08255502292277803</v>
+        <v>0.08143941450490265</v>
       </c>
       <c r="W75">
-        <v>0.216333525594809</v>
+        <v>0.216596586059744</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3302200916911121</v>
+        <v>0.3257576580196107</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2353757124206281</v>
+        <v>0.2372757124206281</v>
       </c>
       <c r="C76">
-        <v>-44.88326395183641</v>
+        <v>-47.46059218375987</v>
       </c>
       <c r="D76">
-        <v>84.01673604816358</v>
+        <v>83.33940781624013</v>
       </c>
       <c r="E76">
-        <v>120.1</v>
+        <v>122</v>
       </c>
       <c r="F76">
-        <v>140.6</v>
+        <v>142.5</v>
       </c>
       <c r="G76">
         <v>11.7</v>
@@ -7519,37 +7519,37 @@
         <v>10.8</v>
       </c>
       <c r="M76">
-        <v>33.15348</v>
+        <v>33.6015</v>
       </c>
       <c r="N76">
-        <v>-22.35348</v>
+        <v>-22.8015</v>
       </c>
       <c r="O76">
-        <v>-5.58837</v>
+        <v>-5.700375</v>
       </c>
       <c r="P76">
-        <v>-16.76511</v>
+        <v>-17.101125</v>
       </c>
       <c r="Q76">
-        <v>-5.065110000000001</v>
+        <v>-5.401125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2888239951400676</v>
+        <v>0.2985449549456703</v>
       </c>
       <c r="T76">
-        <v>3.759503913924635</v>
+        <v>3.90988407048162</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08143941450490265</v>
+        <v>0.08035355564483729</v>
       </c>
       <c r="W76">
-        <v>0.216596586059744</v>
+        <v>0.2168526315789474</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3257576580196107</v>
+        <v>0.3214142225793492</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2372757124206281</v>
+        <v>0.2391757124206281</v>
       </c>
       <c r="C77">
-        <v>-47.46059218375987</v>
+        <v>-50.02708675130177</v>
       </c>
       <c r="D77">
-        <v>83.33940781624013</v>
+        <v>82.67291324869824</v>
       </c>
       <c r="E77">
-        <v>122</v>
+        <v>123.9</v>
       </c>
       <c r="F77">
-        <v>142.5</v>
+        <v>144.4</v>
       </c>
       <c r="G77">
         <v>11.7</v>
@@ -7601,37 +7601,37 @@
         <v>10.8</v>
       </c>
       <c r="M77">
-        <v>33.6015</v>
+        <v>34.04952</v>
       </c>
       <c r="N77">
-        <v>-22.8015</v>
+        <v>-23.24952</v>
       </c>
       <c r="O77">
-        <v>-5.700375</v>
+        <v>-5.81238</v>
       </c>
       <c r="P77">
-        <v>-17.101125</v>
+        <v>-17.43714</v>
       </c>
       <c r="Q77">
-        <v>-5.401125</v>
+        <v>-5.73714</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2985449549456703</v>
+        <v>0.3090759947350732</v>
       </c>
       <c r="T77">
-        <v>3.90988407048162</v>
+        <v>4.072795906751687</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08035355564483729</v>
+        <v>0.07929627201793153</v>
       </c>
       <c r="W77">
-        <v>0.2168526315789474</v>
+        <v>0.2171019390581717</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3214142225793492</v>
+        <v>0.3171850880717262</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2391757124206281</v>
+        <v>0.2410757124206281</v>
       </c>
       <c r="C78">
-        <v>-50.02708675130177</v>
+        <v>-52.58300551414523</v>
       </c>
       <c r="D78">
-        <v>82.67291324869824</v>
+        <v>82.01699448585478</v>
       </c>
       <c r="E78">
-        <v>123.9</v>
+        <v>125.8</v>
       </c>
       <c r="F78">
-        <v>144.4</v>
+        <v>146.3</v>
       </c>
       <c r="G78">
         <v>11.7</v>
@@ -7683,37 +7683,37 @@
         <v>10.8</v>
       </c>
       <c r="M78">
-        <v>34.04952</v>
+        <v>34.49754</v>
       </c>
       <c r="N78">
-        <v>-23.24952</v>
+        <v>-23.69754</v>
       </c>
       <c r="O78">
-        <v>-5.81238</v>
+        <v>-5.924385</v>
       </c>
       <c r="P78">
-        <v>-17.43714</v>
+        <v>-17.773155</v>
       </c>
       <c r="Q78">
-        <v>-5.73714</v>
+        <v>-6.073155</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3090759947350732</v>
+        <v>0.3205227771148591</v>
       </c>
       <c r="T78">
-        <v>4.072795906751687</v>
+        <v>4.249873989653936</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07929627201793153</v>
+        <v>0.07826645030341295</v>
       </c>
       <c r="W78">
-        <v>0.2171019390581717</v>
+        <v>0.2173447710184552</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3171850880717262</v>
+        <v>0.3130658012136518</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2410757124206281</v>
+        <v>0.2429757124206281</v>
       </c>
       <c r="C79">
-        <v>-52.58300551414523</v>
+        <v>-55.12859821305463</v>
       </c>
       <c r="D79">
-        <v>82.01699448585478</v>
+        <v>81.37140178694538</v>
       </c>
       <c r="E79">
-        <v>125.8</v>
+        <v>127.7</v>
       </c>
       <c r="F79">
-        <v>146.3</v>
+        <v>148.2</v>
       </c>
       <c r="G79">
         <v>11.7</v>
@@ -7765,37 +7765,37 @@
         <v>10.8</v>
       </c>
       <c r="M79">
-        <v>34.49754</v>
+        <v>34.94556000000001</v>
       </c>
       <c r="N79">
-        <v>-23.69754</v>
+        <v>-24.14556000000001</v>
       </c>
       <c r="O79">
-        <v>-5.924385</v>
+        <v>-6.036390000000002</v>
       </c>
       <c r="P79">
-        <v>-17.773155</v>
+        <v>-18.10917000000001</v>
       </c>
       <c r="Q79">
-        <v>-6.073155</v>
+        <v>-6.409170000000007</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3205227771148591</v>
+        <v>0.3330101760746254</v>
       </c>
       <c r="T79">
-        <v>4.249873989653936</v>
+        <v>4.44305008009275</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07826645030341295</v>
+        <v>0.07726303427388199</v>
       </c>
       <c r="W79">
-        <v>0.2173447710184552</v>
+        <v>0.2175813765182186</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3130658012136518</v>
+        <v>0.3090521370955279</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2429757124206281</v>
+        <v>0.2448757124206281</v>
       </c>
       <c r="C80">
-        <v>-55.12859821305463</v>
+        <v>-57.66410678691837</v>
       </c>
       <c r="D80">
-        <v>81.37140178694538</v>
+        <v>80.73589321308162</v>
       </c>
       <c r="E80">
-        <v>127.7</v>
+        <v>129.6</v>
       </c>
       <c r="F80">
-        <v>148.2</v>
+        <v>150.1</v>
       </c>
       <c r="G80">
         <v>11.7</v>
@@ -7847,37 +7847,37 @@
         <v>10.8</v>
       </c>
       <c r="M80">
-        <v>34.94556000000001</v>
+        <v>35.39358</v>
       </c>
       <c r="N80">
-        <v>-24.14556000000001</v>
+        <v>-24.59358</v>
       </c>
       <c r="O80">
-        <v>-6.036390000000002</v>
+        <v>-6.148395</v>
       </c>
       <c r="P80">
-        <v>-18.10917000000001</v>
+        <v>-18.445185</v>
       </c>
       <c r="Q80">
-        <v>-6.409170000000007</v>
+        <v>-6.745184999999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3330101760746254</v>
+        <v>0.3466868511257981</v>
       </c>
       <c r="T80">
-        <v>4.44305008009275</v>
+        <v>4.654623893430501</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07726303427388199</v>
+        <v>0.07628502118180755</v>
       </c>
       <c r="W80">
-        <v>0.2175813765182186</v>
+        <v>0.2178119920053298</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3090521370955279</v>
+        <v>0.3051400847272302</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2448757124206281</v>
+        <v>0.2467757124206281</v>
       </c>
       <c r="C81">
-        <v>-57.66410678691837</v>
+        <v>-60.18976567505007</v>
       </c>
       <c r="D81">
-        <v>80.73589321308162</v>
+        <v>80.11023432494993</v>
       </c>
       <c r="E81">
-        <v>129.6</v>
+        <v>131.5</v>
       </c>
       <c r="F81">
-        <v>150.1</v>
+        <v>152</v>
       </c>
       <c r="G81">
         <v>11.7</v>
@@ -7929,37 +7929,37 @@
         <v>10.8</v>
       </c>
       <c r="M81">
-        <v>35.39358</v>
+        <v>35.8416</v>
       </c>
       <c r="N81">
-        <v>-24.59358</v>
+        <v>-25.0416</v>
       </c>
       <c r="O81">
-        <v>-6.148395</v>
+        <v>-6.2604</v>
       </c>
       <c r="P81">
-        <v>-18.445185</v>
+        <v>-18.7812</v>
       </c>
       <c r="Q81">
-        <v>-6.745184999999999</v>
+        <v>-7.081199999999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3466868511257981</v>
+        <v>0.3617311936820879</v>
       </c>
       <c r="T81">
-        <v>4.654623893430501</v>
+        <v>4.887355088102026</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07628502118180755</v>
+        <v>0.07533145841703497</v>
       </c>
       <c r="W81">
-        <v>0.2178119920053298</v>
+        <v>0.2180368421052632</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3051400847272302</v>
+        <v>0.3013258336681398</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2467757124206281</v>
+        <v>0.2486757124206281</v>
       </c>
       <c r="C82">
-        <v>-60.18976567505007</v>
+        <v>-62.70580210554206</v>
       </c>
       <c r="D82">
-        <v>80.11023432494993</v>
+        <v>79.49419789445794</v>
       </c>
       <c r="E82">
-        <v>131.5</v>
+        <v>133.4</v>
       </c>
       <c r="F82">
-        <v>152</v>
+        <v>153.9</v>
       </c>
       <c r="G82">
         <v>11.7</v>
@@ -8011,37 +8011,37 @@
         <v>10.8</v>
       </c>
       <c r="M82">
-        <v>35.8416</v>
+        <v>36.28962</v>
       </c>
       <c r="N82">
-        <v>-25.0416</v>
+        <v>-25.48962</v>
       </c>
       <c r="O82">
-        <v>-6.2604</v>
+        <v>-6.372405</v>
       </c>
       <c r="P82">
-        <v>-18.7812</v>
+        <v>-19.117215</v>
       </c>
       <c r="Q82">
-        <v>-7.081199999999999</v>
+        <v>-7.417214999999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3617311936820879</v>
+        <v>0.3783591512443032</v>
       </c>
       <c r="T82">
-        <v>4.887355088102026</v>
+        <v>5.144584303265291</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07533145841703497</v>
+        <v>0.07440144041188639</v>
       </c>
       <c r="W82">
-        <v>0.2180368421052632</v>
+        <v>0.2182561403508772</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3013258336681398</v>
+        <v>0.2976057616475455</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2486757124206281</v>
+        <v>0.2505757124206281</v>
       </c>
       <c r="C83">
-        <v>-62.70580210554206</v>
+        <v>-65.21243637041582</v>
       </c>
       <c r="D83">
-        <v>79.49419789445794</v>
+        <v>78.88756362958419</v>
       </c>
       <c r="E83">
-        <v>133.4</v>
+        <v>135.3</v>
       </c>
       <c r="F83">
-        <v>153.9</v>
+        <v>155.8</v>
       </c>
       <c r="G83">
         <v>11.7</v>
@@ -8093,37 +8093,37 @@
         <v>10.8</v>
       </c>
       <c r="M83">
-        <v>36.28962</v>
+        <v>36.73764000000001</v>
       </c>
       <c r="N83">
-        <v>-25.48962</v>
+        <v>-25.93764000000001</v>
       </c>
       <c r="O83">
-        <v>-6.372405</v>
+        <v>-6.484410000000001</v>
       </c>
       <c r="P83">
-        <v>-19.117215</v>
+        <v>-19.45323</v>
       </c>
       <c r="Q83">
-        <v>-7.417214999999999</v>
+        <v>-7.753230000000006</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3783591512443032</v>
+        <v>0.3968346596467645</v>
       </c>
       <c r="T83">
-        <v>5.144584303265291</v>
+        <v>5.430394542335586</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07440144041188639</v>
+        <v>0.07349410577271702</v>
       </c>
       <c r="W83">
-        <v>0.2182561403508772</v>
+        <v>0.2184700898587933</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2976057616475455</v>
+        <v>0.2939764230908681</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2505757124206281</v>
+        <v>0.2524757124206282</v>
       </c>
       <c r="C84">
-        <v>-65.21243637041582</v>
+        <v>-67.70988208826954</v>
       </c>
       <c r="D84">
-        <v>78.88756362958419</v>
+        <v>78.29011791173048</v>
       </c>
       <c r="E84">
-        <v>135.3</v>
+        <v>137.2</v>
       </c>
       <c r="F84">
-        <v>155.8</v>
+        <v>157.7</v>
       </c>
       <c r="G84">
         <v>11.7</v>
@@ -8175,37 +8175,37 @@
         <v>10.8</v>
       </c>
       <c r="M84">
-        <v>36.73764000000001</v>
+        <v>37.18566000000001</v>
       </c>
       <c r="N84">
-        <v>-25.93764000000001</v>
+        <v>-26.38566</v>
       </c>
       <c r="O84">
-        <v>-6.484410000000001</v>
+        <v>-6.596415000000001</v>
       </c>
       <c r="P84">
-        <v>-19.45323</v>
+        <v>-19.789245</v>
       </c>
       <c r="Q84">
-        <v>-7.753230000000006</v>
+        <v>-8.089245000000005</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3968346596467645</v>
+        <v>0.4174837572730448</v>
       </c>
       <c r="T84">
-        <v>5.430394542335586</v>
+        <v>5.74982951541415</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07349410577271702</v>
+        <v>0.07260863461882887</v>
       </c>
       <c r="W84">
-        <v>0.2184700898587933</v>
+        <v>0.2186788839568802</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2939764230908681</v>
+        <v>0.2904345384753154</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2524757124206282</v>
+        <v>0.2543757124206281</v>
       </c>
       <c r="C85">
-        <v>-67.70988208826954</v>
+        <v>-70.1983464550808</v>
       </c>
       <c r="D85">
-        <v>78.29011791173048</v>
+        <v>77.70165354491922</v>
       </c>
       <c r="E85">
-        <v>137.2</v>
+        <v>139.1</v>
       </c>
       <c r="F85">
-        <v>157.7</v>
+        <v>159.6</v>
       </c>
       <c r="G85">
         <v>11.7</v>
@@ -8257,37 +8257,37 @@
         <v>10.8</v>
       </c>
       <c r="M85">
-        <v>37.18566000000001</v>
+        <v>37.63368000000001</v>
       </c>
       <c r="N85">
-        <v>-26.38566</v>
+        <v>-26.83368</v>
       </c>
       <c r="O85">
-        <v>-6.596415000000001</v>
+        <v>-6.708420000000001</v>
       </c>
       <c r="P85">
-        <v>-19.789245</v>
+        <v>-20.12526</v>
       </c>
       <c r="Q85">
-        <v>-8.089245000000005</v>
+        <v>-8.425260000000005</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4174837572730448</v>
+        <v>0.4407139921026101</v>
       </c>
       <c r="T85">
-        <v>5.74982951541415</v>
+        <v>6.109193860127535</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07260863461882887</v>
+        <v>0.07174424611146185</v>
       </c>
       <c r="W85">
-        <v>0.2186788839568802</v>
+        <v>0.2188827067669173</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2904345384753154</v>
+        <v>0.2869769844458474</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2543757124206281</v>
+        <v>0.2562757124206281</v>
       </c>
       <c r="C86">
-        <v>-70.19834645508077</v>
+        <v>-72.67803048378239</v>
       </c>
       <c r="D86">
-        <v>77.70165354491922</v>
+        <v>77.1219695162176</v>
       </c>
       <c r="E86">
-        <v>139.1</v>
+        <v>141</v>
       </c>
       <c r="F86">
-        <v>159.6</v>
+        <v>161.5</v>
       </c>
       <c r="G86">
         <v>11.7</v>
@@ -8339,37 +8339,37 @@
         <v>10.8</v>
       </c>
       <c r="M86">
-        <v>37.63368</v>
+        <v>38.0817</v>
       </c>
       <c r="N86">
-        <v>-26.83368</v>
+        <v>-27.2817</v>
       </c>
       <c r="O86">
-        <v>-6.708419999999999</v>
+        <v>-6.820425000000001</v>
       </c>
       <c r="P86">
-        <v>-20.12526</v>
+        <v>-20.461275</v>
       </c>
       <c r="Q86">
-        <v>-8.425259999999998</v>
+        <v>-8.761275000000005</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4407139921026099</v>
+        <v>0.4670415915761172</v>
       </c>
       <c r="T86">
-        <v>6.10919386012753</v>
+        <v>6.5164734508027</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07174424611146187</v>
+        <v>0.07090019615720937</v>
       </c>
       <c r="W86">
-        <v>0.2188827067669173</v>
+        <v>0.21908173374613</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2869769844458475</v>
+        <v>0.2836007846288374</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2562757124206281</v>
+        <v>0.2581757124206281</v>
       </c>
       <c r="C87">
-        <v>-72.67803048378239</v>
+        <v>-75.14912923319403</v>
       </c>
       <c r="D87">
-        <v>77.1219695162176</v>
+        <v>76.55087076680597</v>
       </c>
       <c r="E87">
-        <v>141</v>
+        <v>142.9</v>
       </c>
       <c r="F87">
-        <v>161.5</v>
+        <v>163.4</v>
       </c>
       <c r="G87">
         <v>11.7</v>
@@ -8421,37 +8421,37 @@
         <v>10.8</v>
       </c>
       <c r="M87">
-        <v>38.0817</v>
+        <v>38.52972</v>
       </c>
       <c r="N87">
-        <v>-27.2817</v>
+        <v>-27.72972</v>
       </c>
       <c r="O87">
-        <v>-6.820425000000001</v>
+        <v>-6.932430000000001</v>
       </c>
       <c r="P87">
-        <v>-20.461275</v>
+        <v>-20.79729</v>
       </c>
       <c r="Q87">
-        <v>-8.761275000000005</v>
+        <v>-9.097290000000005</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4670415915761172</v>
+        <v>0.497130276688697</v>
       </c>
       <c r="T87">
-        <v>6.5164734508027</v>
+        <v>6.98193584014575</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07090019615720937</v>
+        <v>0.07007577527166042</v>
       </c>
       <c r="W87">
-        <v>0.21908173374613</v>
+        <v>0.2192761321909425</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2836007846288374</v>
+        <v>0.2803031010866417</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2581757124206281</v>
+        <v>0.2600757124206281</v>
       </c>
       <c r="C88">
-        <v>-75.14912923319403</v>
+        <v>-77.61183202685673</v>
       </c>
       <c r="D88">
-        <v>76.55087076680597</v>
+        <v>75.98816797314328</v>
       </c>
       <c r="E88">
-        <v>142.9</v>
+        <v>144.8</v>
       </c>
       <c r="F88">
-        <v>163.4</v>
+        <v>165.3</v>
       </c>
       <c r="G88">
         <v>11.7</v>
@@ -8503,37 +8503,37 @@
         <v>10.8</v>
       </c>
       <c r="M88">
-        <v>38.52972</v>
+        <v>38.97774</v>
       </c>
       <c r="N88">
-        <v>-27.72972</v>
+        <v>-28.17774</v>
       </c>
       <c r="O88">
-        <v>-6.932430000000001</v>
+        <v>-7.044435000000001</v>
       </c>
       <c r="P88">
-        <v>-20.79729</v>
+        <v>-21.133305</v>
       </c>
       <c r="Q88">
-        <v>-9.097290000000005</v>
+        <v>-9.433305000000004</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.497130276688697</v>
+        <v>0.5318479902801352</v>
       </c>
       <c r="T88">
-        <v>6.98193584014575</v>
+        <v>7.519007827849269</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07007577527166042</v>
+        <v>0.06927030659037696</v>
       </c>
       <c r="W88">
-        <v>0.2192761321909425</v>
+        <v>0.2194660617059891</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2803031010866417</v>
+        <v>0.2770812263615079</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2600757124206281</v>
+        <v>0.2619757124206281</v>
       </c>
       <c r="C89">
-        <v>-77.61183202685673</v>
+        <v>-80.06632266228638</v>
       </c>
       <c r="D89">
-        <v>75.98816797314328</v>
+        <v>75.4336773377136</v>
       </c>
       <c r="E89">
-        <v>144.8</v>
+        <v>146.7</v>
       </c>
       <c r="F89">
-        <v>165.3</v>
+        <v>167.2</v>
       </c>
       <c r="G89">
         <v>11.7</v>
@@ -8585,37 +8585,37 @@
         <v>10.8</v>
       </c>
       <c r="M89">
-        <v>38.97774</v>
+        <v>39.42576</v>
       </c>
       <c r="N89">
-        <v>-28.17774</v>
+        <v>-28.62576</v>
       </c>
       <c r="O89">
-        <v>-7.044435000000001</v>
+        <v>-7.156439999999999</v>
       </c>
       <c r="P89">
-        <v>-21.133305</v>
+        <v>-21.46932</v>
       </c>
       <c r="Q89">
-        <v>-9.433305000000004</v>
+        <v>-9.769319999999997</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5318479902801352</v>
+        <v>0.5723519894701465</v>
       </c>
       <c r="T89">
-        <v>7.519007827849269</v>
+        <v>8.145591813503376</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06927030659037696</v>
+        <v>0.06848314401548633</v>
       </c>
       <c r="W89">
-        <v>0.2194660617059891</v>
+        <v>0.2196516746411483</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2770812263615079</v>
+        <v>0.2739325760619453</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2619757124206281</v>
+        <v>0.2638757124206281</v>
       </c>
       <c r="C90">
-        <v>-80.06632266228638</v>
+        <v>-82.51277961113216</v>
       </c>
       <c r="D90">
-        <v>75.4336773377136</v>
+        <v>74.88722038886783</v>
       </c>
       <c r="E90">
-        <v>146.7</v>
+        <v>148.6</v>
       </c>
       <c r="F90">
-        <v>167.2</v>
+        <v>169.1</v>
       </c>
       <c r="G90">
         <v>11.7</v>
@@ -8667,37 +8667,37 @@
         <v>10.8</v>
       </c>
       <c r="M90">
-        <v>39.42576</v>
+        <v>39.87378</v>
       </c>
       <c r="N90">
-        <v>-28.62576</v>
+        <v>-29.07378</v>
       </c>
       <c r="O90">
-        <v>-7.156439999999999</v>
+        <v>-7.268445000000001</v>
       </c>
       <c r="P90">
-        <v>-21.46932</v>
+        <v>-21.805335</v>
       </c>
       <c r="Q90">
-        <v>-9.769319999999997</v>
+        <v>-10.105335</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5723519894701465</v>
+        <v>0.6202203521492506</v>
       </c>
       <c r="T90">
-        <v>8.145591813503376</v>
+        <v>8.886100160185499</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06848314401548633</v>
+        <v>0.06771367048722243</v>
       </c>
       <c r="W90">
-        <v>0.2196516746411483</v>
+        <v>0.219833116499113</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2739325760619453</v>
+        <v>0.2708546819488897</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2638757124206281</v>
+        <v>0.2657757124206281</v>
       </c>
       <c r="C91">
-        <v>-82.51277961113216</v>
+        <v>-84.95137621069732</v>
       </c>
       <c r="D91">
-        <v>74.88722038886783</v>
+        <v>74.34862378930268</v>
       </c>
       <c r="E91">
-        <v>148.6</v>
+        <v>150.5</v>
       </c>
       <c r="F91">
-        <v>169.1</v>
+        <v>171</v>
       </c>
       <c r="G91">
         <v>11.7</v>
@@ -8749,37 +8749,37 @@
         <v>10.8</v>
       </c>
       <c r="M91">
-        <v>39.87378</v>
+        <v>40.3218</v>
       </c>
       <c r="N91">
-        <v>-29.07378</v>
+        <v>-29.5218</v>
       </c>
       <c r="O91">
-        <v>-7.268445000000001</v>
+        <v>-7.380450000000001</v>
       </c>
       <c r="P91">
-        <v>-21.805335</v>
+        <v>-22.14135</v>
       </c>
       <c r="Q91">
-        <v>-10.105335</v>
+        <v>-10.44135</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6202203521492506</v>
+        <v>0.6776623873641758</v>
       </c>
       <c r="T91">
-        <v>8.886100160185499</v>
+        <v>9.774710176204051</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06771367048722243</v>
+        <v>0.06696129637069774</v>
       </c>
       <c r="W91">
-        <v>0.219833116499113</v>
+        <v>0.2200105263157895</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2708546819488897</v>
+        <v>0.2678451854827909</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2657757124206281</v>
+        <v>0.2676757124206281</v>
       </c>
       <c r="C92">
-        <v>-84.95137621069732</v>
+        <v>-87.38228084725438</v>
       </c>
       <c r="D92">
-        <v>74.34862378930268</v>
+        <v>73.81771915274562</v>
       </c>
       <c r="E92">
-        <v>150.5</v>
+        <v>152.4</v>
       </c>
       <c r="F92">
-        <v>171</v>
+        <v>172.9</v>
       </c>
       <c r="G92">
         <v>11.7</v>
@@ -8831,37 +8831,37 @@
         <v>10.8</v>
       </c>
       <c r="M92">
-        <v>40.3218</v>
+        <v>40.76982</v>
       </c>
       <c r="N92">
-        <v>-29.5218</v>
+        <v>-29.96982</v>
       </c>
       <c r="O92">
-        <v>-7.380450000000001</v>
+        <v>-7.492455000000001</v>
       </c>
       <c r="P92">
-        <v>-22.14135</v>
+        <v>-22.477365</v>
       </c>
       <c r="Q92">
-        <v>-10.44135</v>
+        <v>-10.777365</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6776623873641758</v>
+        <v>0.7478693192935288</v>
       </c>
       <c r="T92">
-        <v>9.774710176204051</v>
+        <v>10.86078908467117</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06696129637069774</v>
+        <v>0.06622545794904172</v>
       </c>
       <c r="W92">
-        <v>0.2200105263157895</v>
+        <v>0.220184037015616</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2678451854827909</v>
+        <v>0.2649018317961669</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2676757124206281</v>
+        <v>0.2695757124206282</v>
       </c>
       <c r="C93">
-        <v>-87.38228084725438</v>
+        <v>-89.80565713156243</v>
       </c>
       <c r="D93">
-        <v>73.81771915274562</v>
+        <v>73.29434286843758</v>
       </c>
       <c r="E93">
-        <v>152.4</v>
+        <v>154.3</v>
       </c>
       <c r="F93">
-        <v>172.9</v>
+        <v>174.8</v>
       </c>
       <c r="G93">
         <v>11.7</v>
@@ -8913,37 +8913,37 @@
         <v>10.8</v>
       </c>
       <c r="M93">
-        <v>40.76982</v>
+        <v>41.21784</v>
       </c>
       <c r="N93">
-        <v>-29.96982</v>
+        <v>-30.41784</v>
       </c>
       <c r="O93">
-        <v>-7.492455000000001</v>
+        <v>-7.60446</v>
       </c>
       <c r="P93">
-        <v>-22.477365</v>
+        <v>-22.81338</v>
       </c>
       <c r="Q93">
-        <v>-10.777365</v>
+        <v>-11.11338</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7478693192935288</v>
+        <v>0.8356279842052203</v>
       </c>
       <c r="T93">
-        <v>10.86078908467117</v>
+        <v>12.21838772025507</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06622545794904172</v>
+        <v>0.065505616014813</v>
       </c>
       <c r="W93">
-        <v>0.220184037015616</v>
+        <v>0.2203537757437071</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2649018317961669</v>
+        <v>0.262022464059252</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2695757124206282</v>
+        <v>0.2714757124206281</v>
       </c>
       <c r="C94">
-        <v>-89.80565713156243</v>
+        <v>-92.2216640669695</v>
       </c>
       <c r="D94">
-        <v>73.29434286843758</v>
+        <v>72.77833593303052</v>
       </c>
       <c r="E94">
-        <v>154.3</v>
+        <v>156.2</v>
       </c>
       <c r="F94">
-        <v>174.8</v>
+        <v>176.7</v>
       </c>
       <c r="G94">
         <v>11.7</v>
@@ -8995,37 +8995,37 @@
         <v>10.8</v>
       </c>
       <c r="M94">
-        <v>41.21784</v>
+        <v>41.66586000000001</v>
       </c>
       <c r="N94">
-        <v>-30.41784</v>
+        <v>-30.86586000000001</v>
       </c>
       <c r="O94">
-        <v>-7.60446</v>
+        <v>-7.716465000000002</v>
       </c>
       <c r="P94">
-        <v>-22.81338</v>
+        <v>-23.14939500000001</v>
       </c>
       <c r="Q94">
-        <v>-11.11338</v>
+        <v>-11.44939500000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8356279842052203</v>
+        <v>0.9484605533773945</v>
       </c>
       <c r="T94">
-        <v>12.21838772025507</v>
+        <v>13.96387168029151</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.065505616014813</v>
+        <v>0.06480125455228812</v>
       </c>
       <c r="W94">
-        <v>0.2203537757437071</v>
+        <v>0.2205198641765705</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.262022464059252</v>
+        <v>0.2592050182091525</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2714757124206281</v>
+        <v>0.2733757124206281</v>
       </c>
       <c r="C95">
-        <v>-92.2216640669695</v>
+        <v>-94.63045621046471</v>
       </c>
       <c r="D95">
-        <v>72.77833593303052</v>
+        <v>72.26954378953531</v>
       </c>
       <c r="E95">
-        <v>156.2</v>
+        <v>158.1</v>
       </c>
       <c r="F95">
-        <v>176.7</v>
+        <v>178.6</v>
       </c>
       <c r="G95">
         <v>11.7</v>
@@ -9077,37 +9077,37 @@
         <v>10.8</v>
       </c>
       <c r="M95">
-        <v>41.66586000000001</v>
+        <v>42.11388000000001</v>
       </c>
       <c r="N95">
-        <v>-30.86586000000001</v>
+        <v>-31.31388000000001</v>
       </c>
       <c r="O95">
-        <v>-7.716465000000002</v>
+        <v>-7.828470000000002</v>
       </c>
       <c r="P95">
-        <v>-23.14939500000001</v>
+        <v>-23.48541000000001</v>
       </c>
       <c r="Q95">
-        <v>-11.44939500000001</v>
+        <v>-11.78541000000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9484605533773945</v>
+        <v>1.098903978940294</v>
       </c>
       <c r="T95">
-        <v>13.96387168029151</v>
+        <v>16.29118362700677</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06480125455228812</v>
+        <v>0.06411187950385952</v>
       </c>
       <c r="W95">
-        <v>0.2205198641765705</v>
+        <v>0.2206824188129899</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2592050182091525</v>
+        <v>0.2564475180154381</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2733757124206281</v>
+        <v>0.2752757124206281</v>
       </c>
       <c r="C96">
-        <v>-94.63045621046471</v>
+        <v>-97.03218382702109</v>
       </c>
       <c r="D96">
-        <v>72.26954378953531</v>
+        <v>71.76781617297891</v>
       </c>
       <c r="E96">
-        <v>158.1</v>
+        <v>160</v>
       </c>
       <c r="F96">
-        <v>178.6</v>
+        <v>180.5</v>
       </c>
       <c r="G96">
         <v>11.7</v>
@@ -9159,37 +9159,37 @@
         <v>10.8</v>
       </c>
       <c r="M96">
-        <v>42.11388000000001</v>
+        <v>42.5619</v>
       </c>
       <c r="N96">
-        <v>-31.31388000000001</v>
+        <v>-31.7619</v>
       </c>
       <c r="O96">
-        <v>-7.828470000000002</v>
+        <v>-7.940475</v>
       </c>
       <c r="P96">
-        <v>-23.48541000000001</v>
+        <v>-23.821425</v>
       </c>
       <c r="Q96">
-        <v>-11.78541000000001</v>
+        <v>-12.121425</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.098903978940294</v>
+        <v>1.309524774728353</v>
       </c>
       <c r="T96">
-        <v>16.29118362700677</v>
+        <v>19.54942035240813</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06411187950385952</v>
+        <v>0.06343701761434523</v>
       </c>
       <c r="W96">
-        <v>0.2206824188129899</v>
+        <v>0.2208415512465374</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2564475180154381</v>
+        <v>0.2537480704573809</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2752757124206281</v>
+        <v>0.2771757124206282</v>
       </c>
       <c r="C97">
-        <v>-97.03218382702109</v>
+        <v>-99.42699303755407</v>
       </c>
       <c r="D97">
-        <v>71.76781617297891</v>
+        <v>71.27300696244593</v>
       </c>
       <c r="E97">
-        <v>160</v>
+        <v>161.9</v>
       </c>
       <c r="F97">
-        <v>180.5</v>
+        <v>182.4</v>
       </c>
       <c r="G97">
         <v>11.7</v>
@@ -9241,37 +9241,37 @@
         <v>10.8</v>
       </c>
       <c r="M97">
-        <v>42.5619</v>
+        <v>43.00992</v>
       </c>
       <c r="N97">
-        <v>-31.7619</v>
+        <v>-32.20992</v>
       </c>
       <c r="O97">
-        <v>-7.940475</v>
+        <v>-8.052479999999999</v>
       </c>
       <c r="P97">
-        <v>-23.821425</v>
+        <v>-24.15744</v>
       </c>
       <c r="Q97">
-        <v>-12.121425</v>
+        <v>-12.45744</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.309524774728353</v>
+        <v>1.625455968410443</v>
       </c>
       <c r="T97">
-        <v>19.54942035240813</v>
+        <v>24.43677544051017</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06343701761434523</v>
+        <v>0.06277621534752913</v>
       </c>
       <c r="W97">
-        <v>0.2208415512465374</v>
+        <v>0.2209973684210527</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2537480704573809</v>
+        <v>0.2511048613901166</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2771757124206282</v>
+        <v>0.2790757124206281</v>
       </c>
       <c r="C98">
-        <v>-99.42699303755407</v>
+        <v>-101.8150259608007</v>
       </c>
       <c r="D98">
-        <v>71.27300696244593</v>
+        <v>70.78497403919926</v>
       </c>
       <c r="E98">
-        <v>161.9</v>
+        <v>163.8</v>
       </c>
       <c r="F98">
-        <v>182.4</v>
+        <v>184.3</v>
       </c>
       <c r="G98">
         <v>11.7</v>
@@ -9323,37 +9323,37 @@
         <v>10.8</v>
       </c>
       <c r="M98">
-        <v>43.00992</v>
+        <v>43.45794</v>
       </c>
       <c r="N98">
-        <v>-32.20992</v>
+        <v>-32.65794</v>
       </c>
       <c r="O98">
-        <v>-8.052479999999999</v>
+        <v>-8.164484999999999</v>
       </c>
       <c r="P98">
-        <v>-24.15744</v>
+        <v>-24.493455</v>
       </c>
       <c r="Q98">
-        <v>-12.45744</v>
+        <v>-12.793455</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.625455968410438</v>
+        <v>2.152007957880584</v>
       </c>
       <c r="T98">
-        <v>24.4367754405101</v>
+        <v>32.58236725401348</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06277621534752913</v>
+        <v>0.06212903786971955</v>
       </c>
       <c r="W98">
-        <v>0.2209973684210527</v>
+        <v>0.2211499728703201</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2511048613901166</v>
+        <v>0.2485161514788783</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2790757124206281</v>
+        <v>0.2809757124206281</v>
       </c>
       <c r="C99">
-        <v>-101.8150259608007</v>
+        <v>-104.1964208494105</v>
       </c>
       <c r="D99">
-        <v>70.78497403919926</v>
+        <v>70.3035791505895</v>
       </c>
       <c r="E99">
-        <v>163.8</v>
+        <v>165.7</v>
       </c>
       <c r="F99">
-        <v>184.3</v>
+        <v>186.2</v>
       </c>
       <c r="G99">
         <v>11.7</v>
@@ -9405,37 +9405,37 @@
         <v>10.8</v>
       </c>
       <c r="M99">
-        <v>43.45794</v>
+        <v>43.90596</v>
       </c>
       <c r="N99">
-        <v>-32.65794</v>
+        <v>-33.10596</v>
       </c>
       <c r="O99">
-        <v>-8.164484999999999</v>
+        <v>-8.276489999999999</v>
       </c>
       <c r="P99">
-        <v>-24.493455</v>
+        <v>-24.82947</v>
       </c>
       <c r="Q99">
-        <v>-12.793455</v>
+        <v>-13.12947</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.152007957880584</v>
+        <v>3.205111936820876</v>
       </c>
       <c r="T99">
-        <v>32.58236725401348</v>
+        <v>48.87355088102021</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06212903786971955</v>
+        <v>0.06149506809553874</v>
       </c>
       <c r="W99">
-        <v>0.2211499728703201</v>
+        <v>0.221299462943072</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2485161514788783</v>
+        <v>0.245980272382155</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2809757124206281</v>
+        <v>0.2828757124206281</v>
       </c>
       <c r="C100">
-        <v>-104.1964208494105</v>
+        <v>-106.5713122205192</v>
       </c>
       <c r="D100">
-        <v>70.3035791505895</v>
+        <v>69.82868777948082</v>
       </c>
       <c r="E100">
-        <v>165.7</v>
+        <v>167.6</v>
       </c>
       <c r="F100">
-        <v>186.2</v>
+        <v>188.1</v>
       </c>
       <c r="G100">
         <v>11.7</v>
@@ -9487,37 +9487,37 @@
         <v>10.8</v>
       </c>
       <c r="M100">
-        <v>43.90596</v>
+        <v>44.35398</v>
       </c>
       <c r="N100">
-        <v>-33.10596</v>
+        <v>-33.55398</v>
       </c>
       <c r="O100">
-        <v>-8.276489999999999</v>
+        <v>-8.388494999999999</v>
       </c>
       <c r="P100">
-        <v>-24.82947</v>
+        <v>-25.165485</v>
       </c>
       <c r="Q100">
-        <v>-13.12947</v>
+        <v>-13.465485</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.205111936820876</v>
+        <v>6.364423873641752</v>
       </c>
       <c r="T100">
-        <v>48.87355088102021</v>
+        <v>97.74710176204042</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06149506809553874</v>
+        <v>0.0608739057915434</v>
       </c>
       <c r="W100">
-        <v>0.221299462943072</v>
+        <v>0.2214459330143541</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.245980272382155</v>
+        <v>0.2434956231661737</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2828757124206281</v>
-      </c>
-      <c r="C101">
-        <v>-106.5713122205192</v>
-      </c>
-      <c r="D101">
-        <v>69.82868777948082</v>
-      </c>
-      <c r="E101">
-        <v>167.6</v>
-      </c>
-      <c r="F101">
-        <v>188.1</v>
-      </c>
-      <c r="G101">
-        <v>11.7</v>
-      </c>
-      <c r="H101">
-        <v>169.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>22.5</v>
-      </c>
-      <c r="K101">
-        <v>11.7</v>
-      </c>
-      <c r="L101">
-        <v>10.8</v>
-      </c>
-      <c r="M101">
-        <v>44.35398</v>
-      </c>
-      <c r="N101">
-        <v>-33.55398</v>
-      </c>
-      <c r="O101">
-        <v>-8.388494999999999</v>
-      </c>
-      <c r="P101">
-        <v>-25.165485</v>
-      </c>
-      <c r="Q101">
-        <v>-13.465485</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.364423873641752</v>
-      </c>
-      <c r="T101">
-        <v>97.74710176204042</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0608739057915434</v>
-      </c>
-      <c r="W101">
-        <v>0.2214459330143541</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2434956231661737</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
